--- a/outputs/weekly/semantic_communication_papers_2026-W20.xlsx
+++ b/outputs/weekly/semantic_communication_papers_2026-W20.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="papers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'papers'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'papers'!$A$1:$X$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:X81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -575,8 +575,8064 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7154102525</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Joint Optimization of Hovering Position and Resource Allocation in UAV-Enabled Semantic Communications via Greedy-Enhanced Adaptive Cellular Genetic Algorithm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pei Liu; Boge Wen</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inventions</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>10.3390/inventions11020040</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/inventions11020040</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.mdpi.com/2411-5134/11/2/40/pdf?version=1775974556</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Despite significant advancements in communication systems, inherent limitations persist in providing reliable data transmission for emerging applications with massive data exchanges. Semantic communication offers promising solutions by extracting and transmitting meaningful information rather than raw bit sequences. However, it faces challenges from high mobility and dynamic channel conditions in wireless environments. In this paper, we design a ground-to-air network architecture that integrates a rotary-wing unmanned aerial vehicle (UAV) and ground terminals to maximize semantic transmission efficiency while maintaining low energy consumption. This approach leverages the high mobility of the UAV for flexible deployment and the data reduction capabilities of semantic communication. Therefore, we formulate a multi-objective optimization problem to simultaneously balance the total semantic transmission rate and the UAV propulsion energy consumption by jointly optimizing the UAV hovering position, semantic encoding lengths, and resource block (RB) allocation. The problem is complex, with mixed continuous and discrete variables, which necessitates an advanced optimization method. To address these challenges, we propose a novel greedy-enhanced adaptive multi-objective cellular genetic algorithm (GEAMOCell), which utilizes an adaptive neighborhood selection mechanism to balance exploration and exploitation, and employs a crowding-guided archive feedback mechanism to maintain population diversity. The simulation results demonstrate that the proposed GEAMOCell algorithm outperforms baseline algorithms in terms of convergence, semantic transmission rate, and energy efficiency.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>DeepSC</t>
+        </is>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>6G / 无线通信</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:17:24.844757+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>arxiv:2605.14940v1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Not All Symbols Are Equal: Importance-Aware Constellation Design for Semantic Communication</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Albert Shaju; Christo Kurisummoottil Thomas; Mayukh Roy Chowdhury</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2605.14940v1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.14940v1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.14940v1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Semantic communication systems for goal-oriented transmission must protect task-relevant information not only through source compression but also via physical layer mapping. Existing approaches decouple constellation design and semantic encoding, exposing critical symbols to channel errors at the same rate as irrelevant ones. Contrary to this, in this paper, a joint semantic-physical layer framework is proposed, which is composed of a vector quantized-variational autoencoder that extracts discrete latent concepts, a semantic criticality indicator (SCI) that scores each concept by task relevance, and a deep reinforcement learning agent that dynamically selects the transmission subset based on instantaneous channel conditions. At the physical layer, a learned semantic-aware M -QAM constellation assigns symbol positions according to joint co-occurrence statistics and SCI scores, departing from the uniform spacing and Gray coding of standard M -QAM which minimizes average BER without regard for semantic content. We introduce a novel semantic symbol vulnerability (SSV) metric and a semantic protection probability (SPP) to quantify the exposure of task-critical symbols to decoding errors, and prove that any Gray-coded constellation is strictly suboptimal in SCI-Weighted SSV whenever the source exhibits non-uniform semantic importance and co-occurrence statistics. Simulation results demonstrate that the proposed constellation achieves near 100% SPP across modulation orders from 4-QAM to 1024-QAM versus 50% for standard constellations at high spectral efficiency, a 21:1 compression ratio with semantic quality above 0.9, generalizing across MNIST, Fashion-MNIST, and FSDD without modification.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic communications; task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>任务导向通信</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Autoencoder / DeepSC</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:29.237416+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>arxiv:2605.05514v1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>When Semantic Communication Meets Queueing: Cross-Layer Latency and Task Fidelity Optimization</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yalin E. Sagduyu; Tugba Erpek</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2605.05514v1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.05514v1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.05514v1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Semantic communication (SemCom) with learned encoder-decoder architectures enables end-to-end learning of compact task-oriented representations optimized for the wireless channel, reducing channel resources needed to convey task-relevant information and improving spectrum efficiency. This paper studies semantic image transmission over block Rayleigh fading with AWGN using a multi-task semantic autoencoder that jointly reconstructs images and predicts labels from the received waveform. The latent dimension (complex channel uses per source sample) serves as a cross-layer control variable governing semantic fidelity and channel resource usage. We characterize the resulting latency-task fidelity tradeoff: larger latent representations improve inference accuracy but increase service time, channel uses, and queueing delay. Building on this insight, we develop online semantic-rate controllers that adapt the latent dimension per update under a long-term semantic error constraint. A queue-aware drift-plus-penalty policy minimizes delay subject to an average semantic error cap, while a complementary age-aware policy minimizes time-average Age of Information (AoI). By adapting the semantic rate to congestion and fidelity requirements, the proposed framework improves spectrum utilization and enables timely semantic updates with significantly lower delay and AoI than fixed-rate baselines.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>6G / 无线通信</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Autoencoder / DeepSC</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>8</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:58.613259+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7160607977</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Research on Multi-Agent Semantic Communication Framework Based on Comparative Learning Joint Optimization</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>H Yang; Hui Li; H Chen; Lijuan Wang; Ji Li; Linbo Qing; Xiaohai He</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10.3390/s26102963</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/s26102963</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.mdpi.com/1424-8220/26/10/2963/pdf?version=1778244292</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>With the rapid development of intelligent services, communication objectives are shifting from humans to multi-agent (MA) systems. This transition necessitates new communication paradigms capable of supporting real-time perception, decision-making, and collaboration among agents. Semantic communication (SeC) focuses on the efficient transmission and accurate understanding of information “meaning” and is well-suited to meet the needs of Mas, such as collaborative perception, reasoning, and decision-making. However, the transmission of semantic information is still constrained by dynamic environments and the diversity of MA tasks. To address these challenges, this work proposes a COmparative learning Joint Optimal (COJO) SeC framework. This work makes three main contributions: first, it jointly optimizes the image reconstruction and classification functions designed for multi-task semantic objectives under different channel conditions, thereby improving the overall task performance of the system; second, based on input image features, compression ratio, task requirements, and channel conditions, an enhanced further compressor is designed, which obtains a training-based mask to significantly reduce the volume of transmitted data; finally, to prevent the loss of key semantic information in multi-task scenarios under channel constraints, it designs a task-driven end-to-end semantic communication training scheme.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DeepSC</t>
+        </is>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>LLM / Agent 辅助语义通信</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Multi-Agent</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>分类/识别</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:17:24.844490+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7152934343</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Semantic Communication with an LLM-enabled Knowledge Base</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wuxia Hu; Caili Guo; Yang Yang; Chunyan Feng; Kuiyuan Ding; Shiwen Mao</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ArXiv.org</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2604.05504</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2604.05504</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2604.05504</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Semantic communication (SC) can achieve superior coding and transmission performance based on the knowledge contained in the semantic knowledge base (KB). However, conventional KBs consist of source KBs and channel KBs, which are often costly to obtain data and limited in data scale. Fortunately, large language models (LLMs) have recently emerged with extensive knowledge and generative capabilities. Therefore, this paper proposes an SC system with LLM-enabled knowledge base (SC-LMKB), which utilizes the generation ability of LLMs to significantly enrich the KB of SC systems. In particular, we first design an LLM-enabled generation mechanism with a prompt engineering strategy for source data generation (SDG) and a cross-attention alignment method for channel data generation (CDG). However, hallucinations from LLMs may cause semantic noise, thus degrading SC performance. To mitigate the hallucination issue, a cross-domain fusion codec (CDFC) framework with a hallucination filtering phase and a cross-domain fusion phase is then proposed for SDG. In particular, the first phase filters out new data generated by the LMKB irrelevant to the original data based on semantic similarity. Then, a cross-domain fusion phase is proposed, which fuses source data with LLM-generated data based on their semantic importance, thereby enhancing task performance. Besides, a joint training objective that combines cross-entropy loss and reconstruction loss is proposed to reduce the impact of hallucination on CDG. Experiment results on three cross-modality retrieval tasks demonstrate that the proposed SC-LMKB can achieve up to 72.6\% and 90.7\% performance gains compared to conventional SC systems and LLM-enabled SC systems, respectively.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DeepSC</t>
+        </is>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>LLM / Agent 辅助语义通信</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>生成</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:17:24.844921+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>arxiv:2605.14300v1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Joint Communication and Computation Design for Mobile Embodied AI Network (MEAN)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chenliang Wu; Zhouxiang Zhao; Jiaxiang Wang; Ruopeng Xu; Chen Zhu; Zhaohui Yang; Zhaoyang Zhang</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2605.14300v1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.14300v1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.14300v1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>This letter investigates the problem of energy efficient collaborative strategy for mobile embodied artificial intelligence network (MEAN) over wireless communication. In the considered model, the agents execute the tasks through collaboration, and they can switch between two operating modes based on the signal-to-noise ratio (SNR) and global collaboration. The dual-mode comprises the base station (BS)-assisted collaborative mode, in which agents make decisions through semantic communication with BS and then collaborate on tasks, and the local computing mode, in which the agents make decisions and execute tasks independently. Due to the dynamic wireless communication and flexible collaboration strategy, we jointly consider computation energy, communication energy, and task-execution energy with specific collaborative gains into a mixed-integer nonlinear programming (MINLP) optimization problem whose goal is to minimize the total system energy consumption. To solve it, we propose a lower-complexity enumeration algorithm: first, we get the optimal closed-form solution for semantic compression ratio and transmit power by proving the strict convexity. Second, we determine the scale of collaboration and the operating mode of each agent by a greedy sorting algorithm based on individual energy-saving potentials. Simulation results show that the proposed algorithm can significantly reduce the total energy consumption compared to benchmark schemes.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic communications</t>
+        </is>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>6G / 无线通信</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Multi-Agent</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:29.237651+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>arxiv:2605.03423v1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Adaptive Dual-Path Framework for Covert Semantic Communication</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Xi Yu; Weicai Li; Lin Yin; Tiejun Lv</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2605.03423v1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.03423v1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.03423v1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>This paper proposes a novel adaptive dual-path framework for covert semantic communication (SemCom), which integrates covert information transmission with task-oriented semantic coding. Unlike conventional covert communication methods that embed hidden messages through power-domain signal superposition, our framework embeds covert data within task-specific features via semantic-level intrinsic encoding. This new architecture introduces dual encoding paths with adaptive block selection: an Explicit path for public task execution and a Stego path that jointly encodes both public and covert information through contrastive representation alignment. A Gumbel-Softmax enabled adaptive path selection mechanism dynamically activates network blocks based on task require- ments. We formulate a multi-objective optimization framework that simultaneously ensures accurate semantic understanding and reliable covert transmission. We rigorously evaluate our framework's security against a powerful, independently trained attacker. Experimental results on the Cityscapes dataset demon- strate a state-of-the-art level of covertness: our method suppresses the attacker's detection accuracy to a near-random guessing level of 56.12%. This robust security is achieved while simultaneously maintaining superior performance on the primary semantic tasks compared to the baselines.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>任务导向通信</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:58.613325+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7160670312</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Spacing-Based Coupling Radiation Control in Pinching-Antennas Systems for Heterogeneous NOMA Users</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ishtiaque Ahmed; Leila Musavian</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ArXiv.org</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2605.04655</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.04655</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.04655</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Pinching-antennas systems (PASS) offer reconfigurable wireless channels via low-cost dielectric mediums by creating line-of-sight (LoS) communication links. Most of the existing PASS cover mechanisms of equal power pinching antennas for conventional bit-based communication, whereas flexible radiation control remains largely unexplored, particularly for heterogeneous semantic and bit users. In this paper, we investigate the performance of semantic communication (SC) using an adjustable radiation model over PASS, where the coupling strength between the dielectric waveguide and each pinching antenna is determined by the antenna-waveguide spacing. Specifically, the non-orthogonal multiple access (NOMA)-assisted heterogeneous users are served by multiple pinching antennas using spacing-controlled adjustable radiation ratios. Uunder this setting, we maximize the semantic spectral efficiency (SE) subject to the bit-user quality of service (QoS) requirement, successive interference cancellation (SIC) feasibility, and the minimum adjacent antennas spacing constraint. An alternating optimization (AO) approach optimizes users power allocation and positions of pinching antennas. Simulations demonstrate the effectiveness of the proportional power PASS model in providing higher semantic SE in different geometrical and numerical settings compared to conventional benchmark schemes.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DeepSC</t>
+        </is>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>6G / 无线通信</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:17:24.844545+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7160565051</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adaptive Dual-Path Framework for Covert Semantic Communication</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Xi Yu; Weicai Li; Lin Yin; Tiejun Lv</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ArXiv.org</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2605.03423</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.03423</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.03423</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>This paper proposes a novel adaptive dual-path framework for covert semantic communication (SemCom), which integrates covert information transmission with task-oriented semantic coding. Unlike conventional covert communication methods that embed hidden messages through power-domain signal superposition, our framework embeds covert data within task-specific features via semantic-level intrinsic encoding. This new architecture introduces dual encoding paths with adaptive block selection: an Explicit path for public task execution and a Stego path that jointly encodes both public and covert information through contrastive representation alignment. A Gumbel-Softmax enabled adaptive path selection mechanism dynamically activates network blocks based on task require- ments. We formulate a multi-objective optimization framework that simultaneously ensures accurate semantic understanding and reliable covert transmission. We rigorously evaluate our framework's security against a powerful, independently trained attacker. Experimental results on the Cityscapes dataset demon- strate a state-of-the-art level of covertness: our method suppresses the attacker's detection accuracy to a near-random guessing level of 56.12%. This robust security is achieved while simultaneously maintaining superior performance on the primary semantic tasks compared to the baselines.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DeepSC</t>
+        </is>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>任务导向通信</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:17:24.844655+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7152933633</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Waveguide to Meaning: Semantic-Aware NOMA for Pinching-Antenna Systems</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ishtiaque Ahmed; Haris Parvaiz; Leila Musavian</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ArXiv.org</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2604.05464</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2604.05464</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2604.05464</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>We investigate the performance of the pinching-antenna systems (PASS) for semantic communication (SC) in both single-waveguide and multi-waveguide scenarios, under the constraints of bit-user quality of service (QoS) and bit-to-semantic decoding order in a heterogeneous users downlink non-orthogonal multiple access (NOMA). Multiple pinching antennas in the single-waveguide scenario are at a minimum adjacent spacing required to prevent mutual coupling. An alternating optimization (AO)-based algorithm optimizes users power allocation coefficients and position of pinching antennas in the single-waveguide NOMA framework. For the multi-waveguide scenario, assuming adjacent waveguides at a sufficient lateral distance apart, the waveguides power allocation subproblem is solved using monotonic optimization and minorization-maximization (MM) approach. Specifically, a lower bound surrogate is iteratively maximized under the feasibility constraints such that a non-decreasing sequence of objective is obtained. Numerical results demonstrate that the NOMA based PASS exploiting SC offers higher semantic spectral efficiency (SE) while fulfilling the bit-user QoS requirement when compared to the considered conventional fixed antenna system. Notably, the multi-waveguide scenario becomes more beneficial for creating adjustable wireless channels in stringentconditions with higher bit-user QoS and wider coverage area requirements.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>DeepSC</t>
+        </is>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>6G / 无线通信</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:17:24.844853+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>arxiv:2605.12681v1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Toward Communication-Efficient Space Data Centers: Bottlenecks, Architectures, and New Paradigms</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Minghao Sun; Zehui Chen; Jinbo Hou; Kezhi Wang; Xiaoli Chu</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2605.12681v1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.12681v1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.12681v1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>The rapid growth of foundation model training and large-scale AI services has driven ground data centers toward unprecedented power densities, intensifying challenges in energy supply, cooling, and spatial scalability. Space Data Centers (SDCs) have emerged as a promising paradigm for hosting energy-intensive computing infrastructures in orbit, leveraging continuous solar energy and radiative cooling advantages. However, unlike ground facilities primarily constrained by power and site availability, SDCs are fundamentally limited by communication capability. The gap between petabit-scale internal data exchange in ground data centers and the gigabit-scale capacity of ground-space links forms a critical bottleneck. This article systematically analyzes communication constraints in SDC architectures and explores semantic communication as a key enabling paradigm. By transmitting compact, task-relevant semantic representations instead of raw data, uplink pressure can be substantially reduced. The feasibility of communication-efficient orbital AI infrastructures is demonstrated through the evaluation of a multi-layer heterogeneous SDC framework consisting of relay satellites and orbital computing nodes operating under coupled energy and thermal constraints. The article further outlines open research challenges toward scalable deployment.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic communications</t>
+        </is>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>LLM / Agent 辅助语义通信</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:29.237809+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7155244845</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Semantic Channel Theory: Deductive Compression and Structural Fidelity for Multi-Agent Communication</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Jianfeng Xu</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>arXiv (Cornell University)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2604.16471</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.16471</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2604.16471</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Shannon's information theory deliberately excludes message semantics. This paper develops a rigorous framework for semantic communication that integrates formal proof systems with Shannon-theoretic tools. We introduce an axiomatic information model comprising Lsem-definable state sets linked by computable enabling maps, and define the semantic channel as a composition of Markov kernels whose supports respect the enabling structure. A fixed proof system induces an irredundant semantic core and a derivation-depth stratification, enabling four distortion measures of increasing semantic depth: Hamming, closure, depth, and a parameterized composite. Six families of computable semantic channel invariants are defined and their inter-relationships established, including a data processing bound, a semantic Fano bound, and an ideal-channel collapse theorem. The central quantitative result is a deductive compression gain: under closure-based fidelity, the minimum block length is determined by the irredundant core size rather than the full knowledge-base size. We instantiate the framework for heterogeneous multi-agent communication, introducing an overlap decomposition that yields necessary and sufficient conditions for closure-reliable communication. A semantic bottleneck phenomenon is identified in broadcast settings: vocabulary mismatch imposes irreducible fidelity limitations even over noiseless carriers. All results are verified on an explicit Datalog instance.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>DeepSC</t>
+        </is>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>LLM / Agent 辅助语义通信</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Multi-Agent</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:17:24.844805+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>arxiv:2605.07354v1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Task-Oriented Communication for Human Action Understanding via Edge-Cloud Co-Inference</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Jingyi Liu; Cheng Yuan; Lijun He; Jun Zhang; Jiawei Shao</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2605.07354v1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.07354v1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.07354v1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>The expanding application of smart sensing has created a growing demand for the accurate understanding of human action at the network edge. Traditional approaches require massive video data to be transmitted from resource-constrained edge devices to powerful cloud servers, incurring prohibitive uplink bandwidth consumption and unacceptable latency while raising privacy concerns. To overcome these bottlenecks, we propose a task-oriented communication framework for human action understanding (TOAU) through edge-cloud collaboration. Our framework utilizes a monocular pose estimator to extract continuous joint coordinates from raw videos, followed by a vector quantized variational autoencoder (VQ-VAE) to convert these coordinates into discrete motion tokens. Consequently, only a compact sequence of codebook indices is transmitted over the network, consuming as few as 9 bits per frame and avoiding privacy leakages. At the cloud server, a lightweight projector aligns these motion tokens with the embedding space of a large vision-language model (VLM) to facilitate complex action understanding, which is trained with an efficient instruction tuning paradigm. Comprehensive evaluations on three benchmarks demonstrate that our TOAU system reduces the transmission payload to approximately 1\% and the system latency to around 20\% compared to video codec-based solutions, while delivering comparable action understanding accuracy.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Autoencoder / DeepSC</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>curated</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:58.613132+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>arxiv:2605.06662v1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Multi-Robot Coordination in V2X Environments</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>John Pravin Arockiasamy; Alexey Vinel</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2605.06662v1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.06662v1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.06662v1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>This paper presents a Vehicle-to-Everything (V2X) communication framework that enables decentralized cooperation among social robots operating in complex urban traffic environments. Building on ETSI Cooperative Awareness and Maneuver Coordination services, the framework introduces two robot-centric facility-layer services: the Robot Awareness Service (RAS) and the Robot Maneuver Coordination Service (RMCS), realized through the Robot Awareness Message (RAM) and the Robot Maneuver Coordination Message (RMCM), respectively. RAS enables role-aware, task-oriented robot awareness while integrating externally detected Vulnerable Road Users (VRUs), including non-V2X pedestrians, into cooperative awareness. RMCS supports event-driven, low-latency coordination of robot maneuvers under explicitly established roles, without centralized infrastructure or prior pairing. A real-world proof of concept demonstrates deterministic multi-robot coordination between a humanoid robot and a quadrupedal robot assisting a pedestrian during a road-crossing scenario, governed by a formally specified finite-state coordination model. Complementary simulations evaluate robot-mediated VRU clustering in mixed V2X environments, showing that RAS-based clustering integrates non-V2X VRUs in safety-critical areas while reducing redundant transmissions from V2X-enabled VRUs, thereby lowering channel load. Together, the proposed services provide a scalable and standards-aligned foundation for integrating cooperative robots into future Connected, Cooperative, and Automated Mobility ecosystems.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>任务导向通信</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:58.613185+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>arxiv:2605.12800v1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Resolution Information: Limits of Ambiguity Resolution for Generative Communication</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Angeles Vazquez-Castro; Faheem Dustin Quazi; Zhu Han</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2605.12800v1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.12800v1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.12800v1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>In generative communication, the transmitter sends a compact generative description, such as model parameters or a latent representation, rather than raw data. The receiver uses this description to form a posterior belief over the underlying state and to resolve semantic ambiguity: which interpretation, decision, or action is supported by the received representation? Inspired by Shannon's geometric view of communication as uncertainty resolution, we introduce resolution information as the minimum information update, measured in nats, required to move the receiver's posterior belief into a low-ambiguity semantic region. Our work yields three main results. First, when the receiver can form any posterior belief, corresponding to the ideal unconstrained case, resolution information reduces to a binary divergence that depends only on each region's prior probability. In this case, the shape of the regions is irrelevant. Under repeated sampling, ambiguity decays exponentially with an exponent equal to the resolution information, giving it an operational meaning as an ambiguity exponent. Second, when the generative representation constrains the posterior family, as in practice, geometry becomes operational and can create irreducible ambiguity floors: half-spaces remain resolvable, whereas polytope-type regions can exhibit residual ambiguity that no amount of additional information can remove. These results reveal a fundamental departure from classical channel coding. In Shannon theory, codes can be designed so that decoding regions separate messages and error probability vanishes below capacity. In generative communication, the model itself induces a constrained posterior geometry that may prevent asymptotic ambiguity resolution. The resulting limit is not on rate, but on resolvability itself.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic communications</t>
+        </is>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>6G / 无线通信</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Hybrid Classical + Neural Coding</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:29.237765+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>arxiv:2605.12491v1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Elastic Attention Cores for Scalable Vision Transformers</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Alan Z. Song; Yinjie Chen; Mu Nan; Rui Zhang; Jiahang Cao; Weijian Mai; Muquan Yu; Hossein Adeli; Deva Ramanan; Michael J. Tarr; Andrew F. Luo</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2605.12491v1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.12491v1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.12491v1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Vision Transformers (ViTs) achieve strong data-driven scaling by leveraging all-to-all self-attention. However, this flexibility incurs a computational cost that scales quadratically with image resolution, limiting ViTs in high-resolution domains. Underlying this approach is the assumption that pairwise token interactions are necessary for learning rich visual-semantic representations. In this work, we challenge this assumption, demonstrating that effective visual representations can be learned without any direct patch-to-patch interaction. We propose VECA (Visual Elastic Core Attention), a vision transformer architecture that uses efficient linear-time core-periphery structured attention enabled by a small set of learned cores. In VECA, these cores act as a communication interface: patch tokens exchange information exclusively through the core tokens, which are initialized from scratch and propagated across layers. Because the $N$ image patches only directly interact with a resolution invariant set of $C$ learned "core" embeddings, this yields linear complexity $O(N)$ for predetermined $C$, which bypasses quadratic scaling. Compared to prior cross-attention architectures, VECA maintains and iteratively updates the full set of $N$ input tokens, avoiding a small $C$-way bottleneck. Combined with nested training along the core axis, our model can elastically trade off compute and accuracy during inference. Across classification and dense tasks, VECA achieves performance competitive with the latest vision foundation models while reducing computational cost. Our results establish elastic core-periphery attention as a scalable alternative building block for Vision Transformers.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic communications</t>
+        </is>
+      </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>图像语义通信</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>分类/识别</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:29.237973+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>arxiv:2605.11301v1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LatentRouter: Can We Choose the Right Multimodal Model Before Seeing Its Answer?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Xueqi Cheng; Yushun Dong</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2605.11301v1</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.11301v1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.11301v1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Multimodal large language models (MLLMs) have heterogeneous strengths across OCR, chart understanding, spatial reasoning, visual question answering, cost, and latency. Effective MLLM routing therefore requires more than estimating query difficulty: a router must match the multimodal requirements of the current image-question input with the capabilities of each candidate model. We propose LatentRouter, a router that formulates MLLM routing as counterfactual multimodal utility prediction. Given an image-question query, LatentRouter extracts learned multimodal routing capsules, represents each candidate MLLM with a model capability token, and performs latent communication between these states to estimate how each model would perform if selected. A distributional outcome head predicts model-specific counterfactual quality, while a bounded capsule correction refines close decisions without allowing residual signals to dominate the prediction. The resulting utility-based policy supports performance-oriented and performance-cost routing, and handles changing candidate pools through shared per-model scoring with availability masking. Experiments on MMR-Bench and VL-RouterBench show that LatentRouter outperforms fixed-model, feature-level, and learned-router baselines. Additional analyses show that the gains are strongest on multimodal task groups where model choice depends on visual, layout-sensitive, or reasoning-oriented requirements, and that latent communication is the main contributor to the improvement. The code is available at: https://github.com/LabRAI/LatentRouter.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>https://github.com/LabRAI/LatentRouter</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>code_url_detected</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>图像语义通信</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:58.612983+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7160726800</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Contextual Memory-Enhanced Source Coding for Low-SNR Communications</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ziqiong Wang; Rongpeng Li</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ArXiv.org</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2605.04400</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.04400</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.04400</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>While Separate Source-Channel Coding (SSCC) retains the practical benefits of modular system design, its effectiveness in noisy text transmission is fundamentally constrained by the fragility of autoregressive source decoding. In low-SNR regimes, even a small number of residual bit errors after channel decoding may derail the subsequent lossless reconstruction process, especially when Arithmetic Coding (AC) relies on Large Language Model (LLM)-based probability estimation. Existing remedies either strengthen channel decoding based solely on channel observations or introduce contextual information only at the receiver for post-hoc correction, yet neither fully addresses the fragility of source probability modeling under residual channel errors. To this end, this paper proposes a Memory-Augmented Source Coding (MASC) scheme for robust SSCC-based transmission. Rather than treating context as external side information, MASC internalizes contextual patterns into a source model shared by both the transmitter-side source encoder and the receiver-side source decoder. Specifically, MASC employs a shared Parameterized Contextual Memory (PCM) to encode multi-order $n$-gram patterns, and further introduces a Mixture-of-Memory-Experts Router (MMER) to perform sparse, hidden-state-dependent routing over memory experts during autoregressive source modeling. By adaptively activating only the most relevant memories at each coding step, MASC refines source probability estimation, shortens average codelength, and mitigates the sensitivity of source decoding to residual channel errors. Extensive experiments over Rayleigh fading and AWGN channels demonstrate the effectiveness of the proposed scheme compared with state-of-the-art methods.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>DeepSC</t>
+        </is>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:17:24.844606+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7137590217</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Role of Social Media Influencers in Promoting Therapeutic Compliance: Implications for Public Health Policy</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Léna Griset; Loïck Menvielle; Rupanwita Dash</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cairn.info</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/journal-gestion-et-management-public-2024-5-page-1b?lang=fr</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Treatment adherence (hereafter, adherence) is critical to achieving positive therapeutic outcomes, whereas non-adherence remains a major public health challenge that hinders recovery and increases healthcare expenditures. As social media has become a prominent channel for information consumption and sharing, social media influencers (SMIs) may play an important role in enhancing adherence. Yet the mechanisms through which engagement with SMIs promotes adherence are not well understood. Drawing on the source attractiveness model, this study posits that influencer characteristics – specifically social attractiveness and perceived credibility – shape evaluations of health messages and, in turn, persuade followers toward adherence. We examine the relationship between SMI social attractiveness and adherence, test the mediating roles of perceived authenticity and perceived expertise, and explore the moderating role of SMI message type. Using survey data from 475 participants, we find that SMI social attractiveness positively predicts treatment adherence, and this effect is mediated by followers’ perceptions of influencer authenticity and expertise. These findings suggest that SMIs can contribute meaningfully to public health communication by encouraging adherence, with the potential to alleviate both fiscal pressures and infrastructural burdens on health systems.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>task-oriented communication; goal-oriented communication</t>
+        </is>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6G / 无线通信</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>综述</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:15:02.018153+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7128031672</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Human-Based Machine Translation Evaluation: A Multi-Dimensional Approach to Sentiment, Emotion, and Argumentation Preservation in Chinese-English Translation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Jingshi Zhou</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Open MIND</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>10.17638/03195263</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7128031672</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.17638/03195263</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>The research landscape of Machine Translation Evaluation (MTE) has traditionally been dominated by automated metrics that, while computationally efficient, often fail to capture the nuanced aspects of translation quality paramount to human users. This dissertation presents a novel human-based evaluation framework specifically developed and validated for Chinese-English machine translation that systematically addresses sentiment, emotion, and argumentation dimensions to address this critical gap in machine translation assessment. The study's theoretical foundation is built upon the premise that effective translation must preserve linguistic accuracy and the underlying emotional resonance, sentiment polarity, and argumentative structures fundamental to human communication. Through a methodologically rigorous approach, this research investigates three primary questions: (1) the suitability of sentiment polarity as a user-oriented feature candidate for MTE, (2) the role of emotion preservation in translation quality assessment, and (3) the significance of maintaining argumentative coherence across language barriers. Our methodological framework employs a multi-phase research design incorporating quantitative and qualitative analyses. The investigation utilizes diverse datasets, including parallel corpora from Classical Chinese Literature, which provide rich emotional content for analysis. The research develops and validates a weighted scoring function that combines Sentiment Analysis (SA) and Argumentation Analysis (AA), calibrated through extensive experimentation and human judgment correlation studies. The findings demonstrate significant advances in three key areas: First, the integration of sentiment analysis reveals substantial improvements in capturing translation nuances that traditional metrics overlook. Second, the emotion analysis component, particularly in examining the preservation of six basic human emotions (happiness, sadness, surprise, fear, anger, and disgust), provides crucial insights into translation fidelity. Third, the argumentation analysis framework offers a novel approach to evaluating the preservation of logical structures and persuasive elements in translated texts. This research makes several original contributions to the field: (1) it establishes a comprehensive human-based evaluation framework that transcends traditional automated metrics, (2) it develops innovative methodologies for integrating affective and argumentative dimensions into translation assessment, and (3) it provides empirical evidence for the effectiveness of multi-dimensional evaluation approaches in capturing human-centric translation quality aspects. The implications of this work go beyond theoretical advancements, providing practical applications for enhancing machine translation systems and evaluation methods. Future research directions include investigating additional user-focused features, improving weighting mechanisms for various user groups, and applying this framework to other natural language processing tasks.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:15:02.018275+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7133106184</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Investigating the roles of cognition and speech production in older adults' social engagement</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Laura Manderson; Louise A. Brown Nicholls; Anja Kuschmann; Anja Lowit</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Open MIND</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://osf.io/cew63</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://osf.io/cew63</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Older age is associated with changes to cognitive functioning and communicative ability (Salthouse, 2019; Shadden &amp;amp; Toner, 1997). Both are important for maintaining an active lifestyle into older age (e.g. Borgeest et al., 2020; Palmer et al., 2019), which is in turn beneficial for brain health (Hertzog et al., 2008; Park &amp;amp; Reuter-Lorenz, 2009). As such, activity engagement is frequently reported as being an indicator of successful ageing (Douglas et al., 2017; Reuter- Lorenz &amp;amp; Park, 2009). Frequency of engagement in social, physical and intellectual activities protects against age-related cognitive decline (e.g. Borgeest et al., 2020; Lövdén et al., 2005; Oh et al., 2021). However, the World Health Organisation (2021) has reported that loneliness in older adults is increasing due to lack of social connectedness. This is concerning, particularly as loneliness is a risk factor for early mortality and could be more dangerous than smoking and alcohol use (Holt Lunstad et al., 2015). Research shows that the potential barriers to older adults’ participation include changes to health and cognitive factors (Townsend et al., 2021). For example, older adults with and without speech and/or voice difficulties report reduced social participation (Meeker et al., 2021; Palmer et al., 2019; Verdonck-de Leeuw &amp;amp; Mahiew, 2004), suggesting that older adults are potentially at risk of reduced social engagement and cognitive decline. Given that social engagement is crucial for health and wellbeing, it is important to investigate whether cognitive and/or communication changes affect social engagement in older age. Older adults experience gradual changes to ‘fluid’ cognitive abilities including reasoning, memory, spatial orientation, and perceptual speed, which can start to become apparent around age 60 – 65 (Salthouse, 2019; Schaie, 2005). ‘Crystallised’ abilities, on the other hand, refer to learned skills such as verbal/numerical knowledge and semantic memory. These abilities tend to remain stable or even show improvement across the lifespan (Salthouse, 2010). There is also evidence of age-related differences between younger and older adults on a range of motor speech outcomes including speech and articulation rates (Duchin &amp;amp; Mysak, 1987; Parnell &amp;amp; Amerman, 1987), speech timing (Amerman &amp;amp; Parnell, 1992) voice quality (Rojas et al., 2020; Tucker et al., 2021) and articulatory accuracy (Bilodeau-Mercure &amp;amp; Tremblay, 2016). How these functional changes interact and impact day to day social engagement in older adults has not been investigated. Theoretically, the Scaffolding Theory of Ageing and Cognition (STAC; Reuter-Lorenz &amp;amp; Park, 2009) predicts that modifiable lifestyle factors such as social and intellectual engagement influence the extent to which older adults can compensate for reduced cognitive resources. Indeed, higher levels of activity engagement are associated with better cognitive health (e.g. Lövdén et al., 2005; Oh et al., 2021; Small et al., 2012). However, there could be a bidirectional relationship between activity engagement and cognition, particularly when considering social participation (Casey et al., 2021; Lovden et al., 2005; Small et al., 2012). Specifically, cognitive ability could also predict the extent to which older adults engage socially. Furthermore, in older adults with and without disordered speech, several studies have found that self-reported speech changes are associated with a reduction in social networks and activities (Cruice et al., 2005; Nagayoshi et al., 2017; Palmer et al., 2016, 2019b; Verdonck-de Leeuw &amp;amp; Mahieu, 2004). This suggests that age-related speech and/or cognitive changes could potentially act as a barrier to social engagement, which, in turn, is believed to be beneficial for brain health. The aim of this project is to explore potential relationships amongst objective measures of cognition and speech, and subjective reports of social engagement. Social engagement is a multi-faceted construct and has been used interchangeably with terms such as ‘social support’, ‘social participation’, ‘social integration’ and ‘social relations’ (Fuller-Iglesias &amp;amp; Rajbhandari, 2016). Previous research has conceptualised the social aspect of people’s lives by measuring the size of social networks, types of social support, closeness of social relations and frequency of activity involvement (Cruice et al., 2005; Fuller-Iglesias &amp;amp; Rajbhandari, 2016; Nagayoshi et al., 2017; Palmer et al., 2019b; Small et al., 2012). Regarding speech production, communicative participation is a key construct (Eadie et al., 2006) and shows links with speech intelligibility and cognition (Barnish et al., 2017). Therefore, we aim to explore the following research questions: RQ 1 : To what extent do objective measures of cognition and/or speech predict frequency of activity engagement? RQ 2: To what extent do objective measures of cognition and/or speech predict social network size? RQ 3. To what extent do objective measures of cognition and/or speech predict communicative participation?</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>semantic communication</t>
+        </is>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>语音语义通信</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Speech</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:32.829909+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>arxiv:2605.14651v1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TERRA-CD: Multi-Temporal Framework for Multi-class and Semantic Change Detection</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Omkar Oak; Rukmini Nazre; Rujuta Budke; Suraj Sawant</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2605.14651v1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.14651v1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.14651v1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Urban vegetation monitoring plays a vital role in understanding environmental changes, yet comprehensive datasets for this purpose remain limited. To address this gap, we present the Temporal Remote-sensing Repository for Analyzing Change Detection (TERRA-CD), a benchmark dataset comprising 5,221 Sentinel-2 image pairs from 2019 and 2024, covering 232 cities across the USA and Europe. The dataset features three distinct annotation schemes: 4-class land cover mapping masks, 3-class vegetation change masks, and 13-class semantic change masks capturing all possible land cover transitions. Using various deep learning approaches including Siamese networks, STANet variants, Bi-SRNet, Changemask, Post-Classification Comparison, and HRSCD strategies, we evaluated the dataset's effectiveness for both vegetation Multi-class Change Detection as well as Semantic Change Detection. The proposed dataset and methods are available at https://github.com/omkarsoak/TERRA-CD.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>semantic communication</t>
+        </is>
+      </c>
+      <c r="M23" t="b">
+        <v>1</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://github.com/omkarsoak/TERRA-CD</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>code_url_detected</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>图像语义通信</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>分类/识别</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:29.237534+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>arxiv:2605.14650v1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Multimodal Learning for MIMO Beam Prediction Based on Variational Inference</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Zijian Zheng; Wenqiang Yi; Hyundong Shin; Arumugam Nallanathan</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2605.14650v1</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.14650v1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.14650v1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Accurate beam prediction is essential for mitigating signalling overhead and latency in integrated sensing and communication-enabled massive multi-input multi-output systems. With the aid of multimodal learning, the prediction accuracy can be enhanced by leveraging the complementary information from other existing sensors, but the practical deployment is often constrained by the high cost of acquiring semantically aligned multimodal datasets. This paper proposes a variational-inference-based multimodal framework that decouples the optimization problem into modular feature extraction and cross-modal semantic alignment. Specifically, we develop a two-stage training strategy where the model utilises abundant unimodal data for representation learning before performing refined alignment on limited multimodal samples. This design enhances data efficiency and ensures robust feature fusion under sensing uncertainties. Experimental results on the DeepSense6G dataset demonstrate that the proposed framework achieves competitive beam prediction accuracy and maintains high reliability, while only requiring 20% of the multimodal training data compared to conventional end-to-end benchmarks.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic communications</t>
+        </is>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>6G / 无线通信</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Multimodal</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:29.237601+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7161171696</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Contexts of Violence against Physicians in the Health System: A Grounded Theory Study in Ahvaz Medical Centers</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ziba Damadam; Hossein Afrasiani</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DOAJ (DOAJ: Directory of Open Access Journals)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>10.22108/srspi.2025.146253.2143</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://doaj.org/article/acd58a228b7c454c9214db73a38e0c5d</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://doaj.org/article/acd58a228b7c454c9214db73a38e0c5d</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Introduction Violence against medical staff is a persistent and multifaceted challenge in contemporary healthcare systems. Its origins extend beyond individual behavior, rooted in broader social, cultural, and organizational structures. This phenomenon manifests in forms ranging from verbal aggression to physical assault with significant adverse consequences: it degrades the quality of medical services and patient satisfaction while severely impacting the psychological well-being and job motivation of healthcare workers. From a sociological perspective, violence in healthcare settings constitutes a social fact. It emerges from structural tensions, unequal power dynamics, unmet expectations, and the growing complexity of interactions between medical staff and patients or their companions. In recent years, this issue has intensified, gaining greater visibility through the rise of anti-physicianism—a social attitude marked by distrust, hostility, and a decline in the traditional symbolic respect afforded to medical professionals. Such attitudes contribute to escalating conflicts in clinical environments, complicating communication, decision-making, and the daily functioning of treatment teams. These outcomes ultimately weaken institutional performance and undermine public trust in the healthcare system. The primary goal of this research was to explore how medical staff perceive, interpret, and experience violence within hospitals and medical centers. By uncovering the underlying social dynamics, meanings, and behavioral patterns that shape such incidents, this study aimed to provide insights that can inform effective policy-making, targeted training programs, and significant organizational reforms. Materials &amp; Methods This study adopted a qualitative research design, utilizing a grounded theory approach to investigate the dynamics of violence and anti-physicianism within medical centers in Ahvaz. Data were collected through semi-structured interviews with 30 medical staff members from hospitals affiliated with Ahvaz University of Medical Sciences. Participants were selected via purposive sampling and interviews continued until theoretical saturation was achieved. The data analysis followed the systematic stages of grounded theory: open, axial, and selective coding. This analytical process revealed that violence against medical staff stemmed from the complex interplay of structural, cultural, and professional factors. These factors were conceptualized into 11 core categories: 1) normalization of violence; 2) eroding bureaucracy; 3) lack of resilience and empathy; 4) discursive contradiction; 5) transition from patriarchal to patient-centered medicine; 6) the absent doctor; 7) negative media representation; 8) medical distancing; 9) the distrust gap; 10) burnout; 11) the dilemma of leaving the profession or migrating. Together, these categories constituted the principal domains, through which the vicious cycle of anti-physicianism was reproduced. Discussion of Results &amp; Conclusion The interview findings demonstrated that violence against healthcare workers transcended individual or psychological explanations; it was fundamentally a manifestation of broader structural inequalities and institutional crises. This violence was sustained by an institutionalized culture embedded within wider societal norms and by dominant assumptions that normalized and justified aggression. Moreover, it was rooted in the specific social fabric of cultural regions, reflecting deep-seated systemic failures within both the healthcare system and society at large (Pavlova &amp; Geretto, 2018). Effectively addressing this phenomenon necessitated comprehensive reforms in health policy. Key interventions included: Strengthening institutional and financial support for healthcare workers Promoting a positive and accurate public representation of their social status Criminalizing violence and developing effective legal deterrents Transitioning toward participatory, community-oriented models of doctor-patient interaction Implementing such strategies can cultivate social resilience and empathy, laying a foundation for reducing violence in clinical settings. Ultimately, violence against medical personnel is not merely an organizational or systemic dysfunction; it constitutes a profound semantic and symbolic crisis within the healthcare relationship. Responding to this complexity demands an integrated theoretical approach. This should incorporate Weber’s focus on the ethical intentions guiding actors; Derrida’s insights into the discursive hierarchies of modern medicine; Giddens’s structuration theory to understand how agents reproduce and transform systemic structures; and Parsonian principles to restore the normative balance in the doctor-patient role-set. Together, these perspectives illuminate the multilayered nature of violence in healthcare and can inform the design of significant, context-sensitive interventions.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>semantic communication</t>
+        </is>
+      </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:32.830415+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>arxiv:2605.07358v1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A Comprehensive Survey on Agent Skills: Taxonomy, Techniques, and Applications</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Yingli Zhou; Wang Shu; Yaodong Su; Wenchuan Du; Yixiang Fang; Xuemin Lin</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2605.07358v1</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.07358v1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.07358v1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Large language model (LLM)-based agents that reason, plan, and act through tools, memory, and structured interaction are emerging as a promising paradigm for automating complex workflows. Recent systems such as OpenClaw and Claude Code exemplify a broader shift from passive response generation to action-oriented task execution. Yet as agents move toward open-ended, real-world deployment, relying on from-scratch reasoning and low-level tool calls for every task become increasingly inefficient, error-prone, and hard to maintain. This survey examines this challenge through the lens of \emph{agent skills}, which we define as reusable procedural artifacts that coordinate tools, memory, and runtime context under task-specific constraints. Under this view, agents and skills play complementary roles: agents handle high-level reasoning and planning, while skills form the operational layer that enables reliable, reusable, and composable execution. Skills are therefore central to the scalability, robustness, and maintainability of modern agent systems. We organize the literature around four stages of the agent skill lifecycle -- representation, acquisition, retrieval, and evolution -- and review representative methods, ecosystem resources, and application settings across each stage. We conclude by discussing open challenges in quality control, interoperability, safe updating, and long-term capability management. All related resources, including research papers, open-source data, and projects, are collected for the community in \textcolor{blue}{https://github.com/JayLZhou/Awesome-Agent-Skills}.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://github.com/JayLZhou/Awesome-Agent-Skills</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>code_url_detected</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>LLM / Agent 辅助语义通信</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>综述</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:58.613087+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>arxiv:2604.27854v1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NetSatBench: A Distributed LEO Constellation Emulator with an SRv6 Case Study</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Andrea Detti; Shahram Dadras; Giuseppe Tropea</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2604.27854v1</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2604.27854v1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2604.27854v1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NetSatBench is a distributed emulation platform for evaluating communication protocols and application workloads over large-scale LEO satellite systems. Satellites, gateways, and user terminals are implemented as Linux containers distributed across a cluster of bare-metal or virtual machines, while emulated links are realized through a Layer-2 VXLAN overlay. The system state is maintained in an Etcd key-value store and updated through epoch files, which propagate link and task changes to local control agents running inside the emulated nodes. In contrast to library-oriented tools that require users to write control programs, NetSatBench adopts a higher-level declarative workflow based on JSON "scenario files" and a command-line interface. The platform decouples physical-layer and routing modeling from the emulator core through external plug-ins, while providing built-in support for IPv4 and IPv6 routing, including IS-IS and ideal time-varying routing. Rather than focusing on emulator micro-performance alone, we illustrate what NetSatBench enables through an SRv6-based LEO architecture in which control procedures manage data tunnels between users and gateways under different handover policies. This case study shows how NetSatBench can support protocol-level experimentation under time-varying LEO dynamics and highlights the importance of end-to-end handover strategies that jointly account for the satellites serving both the user and the gateway.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>LLM / Agent 辅助语义通信</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:58.613424+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7161056467</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>QISFP: Quantum-Inspired Semantic Fidelity for Energy-Efficient and Noise-Resilient Visual IoT Transmission</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>David Emmanuel; Anil Fernando</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Research Square</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>10.21203/rs.3.rs-8273777/v1</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.21203/rs.3.rs-8273777/v1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.researchsquare.com/article/rs-8273777/latest.pdf</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>DeepSC</t>
+        </is>
+      </c>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>图像语义通信</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:17:24.844403+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7155451972</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SAGE: Training-Free Semantic Evidence Composition for Edge-Cloud Inference under Hard Uplink Budgets</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Inhyeok Choi; Hyuncheol Park</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ArXiv.org</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2604.19623</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.19623</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2604.19623</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Edge-cloud hybrid inference offloads difficult inputs to a powerful remote model, but the uplink channel imposes hard per-request constraints on the number of bits that can be transmitted. We show that selecting transmitted content based solely on attention-based importance, the standard approach in collaborative inference, is inherently limited under hard budgets. Two findings support this claim. First, replacing high-importance units with low-importance but complementary ones improves server accuracy. This shows that what matters is not individual importance but how well the transmitted set covers diverse aspects of the input. Second, spatially uniform selection without any content information achieves competitive accuracy at moderate budgets. This confirms that spatial coverage alone carries independent value. Based on this analysis, we propose SAGE (Semantic Attention-Guided Evidence), a principled, training-free method that combines importance filtering with embedding-diversity sampling. SAGE achieves 93% of the server ceiling in offloaded accuracy while transmitting fewer than half of the available evidence units on ImageNet-1K, substantially outperforming importance-only composition.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DeepSC</t>
+        </is>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>图像语义通信</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:17:24.844698+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7160576152</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Robots' Inner Speech meets Thories of emotion: towards Affective Robotics in Human Robot Interaction</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sophia Corvaia</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Nova Science Publishers (Nova Science Publishers, Inc.)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://hdl.handle.net/10447/705548</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://iris.unipa.it/bitstream/10447/705548/2/Tesi%20Finale%20Sophia%20Corvaia.pdf</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Robotics is undergoing a paradigm shift, evolving from systems primarily designed to execute mechanical or repetitive tasks into autonomous agents capable of engaging in meaningful, socially coherent interactions with humans.As robots become increasingly integrated into everyday environments, ranging from domestic assistance to healthcare, education, and therapeutic contexts, the demand for machines capable of understanding, expressing, and regulating emotions has grown considerably.Emotional intelligence is no longer perceived as an optional layer for enhancing user experience; it is increasingly recognised as a core requirement for establishing trust, fostering long-term interaction, and enabling cooperation between humans and artificial agents.Nevertheless, implementing this capability computationally is a significant challenge that demands the integration of affective modeling, cognitive architectures, and communication systems.Emotions in biological organisms serve as a crucial mediator between cognitive processes and environmental demands.They influence decision-making, guide attention, facilitate memory consolidation, and play a key role in social bonding.From an evolutionary perspective, emotions act as adaptive responses that help organisms prioritise goals, evaluate risks, and coordinate behaviour within complex social structures.Translating these mechanisms into artificial systems involves not only developing mathematical models of affective states but also integrating them into architectures that enable flexible, context-sensitive behaviour.Many existing approaches in affective computing remain primarily reactive, mapping external stimuli to predefined emotional outputs, often yielding limited or shallow expressions that lack introspective depth.This doctoral research aims to address these limitations by introducing a novel paradigm that integrates computational emotional models with inner speech mechanisms.Inner speech, also known as self-talk or covert verbal thinking, is a welldocumented phenomenon in human cognition that contributes to self-regulation, planning, problem-solving, and emotional adjustment.In humans, inner speech enables the simulation of social dialogue within the self, allowing individuals to reason about Abstract their feelings, anticipate consequences, and regulate their reactions in real time.The central hypothesis of this dissertation is that endowing robots with an analogous internal dialogue mechanism can support a form of machine introspection that enhances both emotional coherence and transparency in interaction.This introspection lays the foundation for robot consciousness, explored in detail in Chapter 2.The research presented in this dissertation demonstrates that the integration of inner speech into computational emotional models provides a viable pathway toward more reflective and communicative robotic systems.Rather than focusing solely on emotional expression, the proposed approach enables robots to reflect upon, regulate, and communicate their internal states in a manner that is intelligible and socially appropriate for human partners.The findings suggest that such models can enhance the quality of human-robot interaction across multiple domains, while contributing to user trust and system acceptability.Future research will explore the scalability of this approach to more complex emotional repertoires, its integration with adaptive learning mechanisms, and its ethical implications, particularly regarding transparency, accountability, and the anthropomorphisation of artificial agents.The dissertation is organised to reflect both its theoretical foundations and its applied contributions.The initial chapters review the state of the art in affective computing, emotion modelling, and inner speech, and outline the methodological choices underlying the proposed computational models.The central chapters detail the system architecture, its integration into robotic platforms, and the results of controlled experimental evaluations.The final chapters focus on real-world applications, describing interaction design, evaluation criteria, and insights gained from deployment in practical settings.The first part of the research focuses on the design and formalisation of computational models capable of generating and modulating emotional states through mechanisms of inner speech.These models adopt a hybrid architecture that combines symbolic reasoning with dynamic affective processes, enabling a bidirectional flow between cognitive appraisals and emotional expressions.In Chapter 1, the thesis introduces the conceptual and computational integration of inner speech within an appraisal-based emotional model for robots.Building on appraisal theories, which describe emotions as emerging from cognitive evaluations of situational variables, this chapter examines how self-directed dialogue can serve as an internal mechanism that supports emotional computation.Inner speech is modelled as a structured process of self-reflection that enables the robot to focus on contextually relevant information, compute assessment variables, and generate emotionally coherent responses.Particular attention is devoted to analysing emotional dynamics under stressful conditions, demonstrating that the proposed model produces patterns Abstract consistent with those observed in healthy adults.Furthermore, the chapter discusses how the externalisation of inner reasoning through think-aloud behaviour can improve transparency and coordination in collaborative tasks, supporting clearer joint decisionmaking and mutual understanding between human and robot partners.In Chapter 2, the research extends the investigation from appraisal-based evaluation to a broader affective framework grounded in Damasio's theory, in which emotions arise from the dynamic interaction between bodily-like signals and cognitive processes.This chapter explores how a robot can move beyond mere detection or simulation of emotions toward a computational architecture that supports emotionally grounded responses mediated by inner speech.Self-directed dialogue is implemented as a mechanism that enables the robot to articulate its interpretation of contextual events and its internal state, thereby fostering the emergence of more coherent and interpretable behaviours.The model is deployed on a real robotic platform, and experimental findings demonstrate that human participants interacting with the system can perceive the robot's emotional states.The results highlight how integrating embodied-cognitive mechanisms with inner speech enhances perceived empathy, trust, and engagement in Human-Robot Interaction.Building on this foundation, the second part of the dissertation shifts focus to a preliminary investigation of the application of the developed computational models in a medical context.In Chapter 3, the thesis places the developed models in a complex, high-risk collaborative environment, with a specific focus on a medical application.The chapter examines the role of robotic inner speech in cooperation with a nurse during the preparation of a surgical table, a task that requires precision and careful instrument placement to avoid adverse procedural outcomes.The study analyses how the robot's self-directed dialogue contributes to reassurance and stress management in demanding contexts, while simultaneously enhancing clarity and understanding of task-related instructions.The findings demonstrate that inner speech retains its effectiveness in more complex and high-stakes interaction settings, supporting transparency, trustworthiness, and performance under elevated cognitive and emotional demands.From a broader perspective, this work advances affective and cognitive robotics by introducing a mechanism that bridges the gap between reactive emotional systems and reflective, self-regulating architectures.Traditional models often rely on surfacelevel mappings between external events and emotional displays, resulting in behaviours that may appear expressive but lack the deeper coherence that characterises human affective life.By incorporating inner speech, the models developed in this dissertation enable robots to engage in self-referential processing, thereby enriching their emotional landscape and enhancing their social presence.This integration opens new avenues for research on how artificial agents can develop and maintain internal narratives, how</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>semantic channel coding</t>
+        </is>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>综述</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:21:37.635509+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7160970277</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Measuring Islamic Republic Propaganda in Western Media Coverage of Iran: A Computational Framework</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Leila Habibi</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CUNY Academic Works (City University of New York)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://academicworks.cuny.edu/gc_etds/6675</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://academicworks.cuny.edu/context/gc_etds/article/7911/viewcontent/Measuring_Islamic_Republic_Propaganda_in_Western_Media_Coverage_o.pdf</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Detecting propaganda is fundamentally difficult: effective propaganda must simultaneously conceal persuasive intent while achieving persuasive effect, which means that sophisticated propagandistic discourse necessarily occupies the ambiguous middle of a rhetorical spectrum rather than its obvious extremes. This thesis defines this property as the dual constraint problem and argues that it poses two challenges for the binary classification framing that dominates propaganda detection in Natural Language Processing (NLP). First, propaganda by definition does not come with clear labels: no propaganda arm willingly accepts the designation, so reliable ground truth does not exist at the source. Second, because the producer is actively concealing intent, the surface features of any article — including the choice of topic itself — can be chosen adversarially to evade the very signals a binary classifier would rely on. This thesis builds a framework for propaganda measurement that takes the estimated probabilities from a binary classification task and adjusts for topic, isolating propaganda-related components of text such as framing and narrative from subject matter. The framework is applied to the information environment surrounding the Islamic Republic of Iran, using two institutionally opposed outlets as training corpora: Press TV, the English-language channel of Islamic Republic of Iran Broadcasting, and Iran International, a Persian-language satellite channel positioned in opposition to the Iranian state. A Latent Dirichlet Allocation topic model characterizes the topical structure of the two corpora, and inverse-probability weighting (IPW) debiases the resulting estimators. Eight classifiers, combining TF-IDF n-gram and sentence-transformer representations with and without IPW, are treated as alternative estimators of rhetorical alignment, yielding two measurement instruments: the Raw Propaganda Score (RPS) and the Topic-Adjusted Propaganda Score (TAPS). Applied to an external corpus of 1,414 articles by ten journalists covering Iranian affairs in Western media, TAPS diverges substantially from RPS and produces a structural reordering of journalist rankings that aligns far more closely with independent external benchmarks — including institutional affiliation and an independently produced activist classification of regime-aligned media figures — providing external validity for the framework and its measurements.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>semantic channel coding</t>
+        </is>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>分类/识别</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:21:37.635643+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7137612268</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Le rôle des influenceurs des médias sociaux dans la promotion de l’observance thérapeutique : enjeux et perspectives pour la santé publique</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Léna Griset; Loïck Menvielle; Rupanwita Dash</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Cairn.info</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/revue-gestion-et-management-public-2026-0-page-1b?lang=fr</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>L’adhésion au traitement médical revêt une importance capitale pour l’obtention de résultats positifs, tandis que la non-adhésion représente un défi majeur en matière de santé publique, entravant le processus de guérison. À l’ère des réseaux sociaux, devenus un moyen incontournable de consommation et de partage d’informations, les influenceurs peuvent jouer un rôle essentiel dans l’amélioration de l’observance thérapeutique. Cependant, les mécanismes sous-jacents demeurent insuffisamment compris. Cette étude, basée sur le modèle de l’attractivité de la source, émet l’hypothèse que les caractéristiques des influenceurs, telles que leur attrait social et leur crédibilité perçues, peuvent susciter une évaluation positive de leurs messages liés à la santé, incitant ainsi leur communauté à suivre le traitement recommandé. Ainsi, notre recherche explore la relation entre l’attrait social des influenceurs et l’adhésion au traitement, en prenant en compte le rôle médiateur de l’authenticité et de l’expertise perçues, tout en analysant l’effet modérateur du type de message relayé par ces influenceurs. Les données issues d’une enquête menée auprès de 475 participants révèlent que l’attrait social des influenceurs exerce un impact positif sur l’adhésion au traitement parmi les utilisateurs. De plus, cette relation est médiée par la perception de l’authenticité et de l’expertise des influenceurs. En conséquence, ces résultats suggèrent que les influenceurs jouent un rôle crucial dans la communication en matière de santé publique, en encourageant leurs abonnés à adhérer à leur traitement. Cette contribution pourrait de fait potentiellement alléger la charge financière et logistique pesant sur le système de santé publique actuel.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>task-oriented communication; goal-oriented communication</t>
+        </is>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:15:02.018411+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>arxiv:2605.14188v1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>QOuLiPo: What a quantum computer sees when it reads a book</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Christophe Jurczak</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2605.14188v1</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.14188v1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.14188v1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>What does a book look like to a quantum computer? This paper takes eight classical works of the Renaissance and its late-antique inheritance -- from Augustine to Galileo -- and runs each through a neutral-atom quantum processor. The bridge is graphs: each textual unit becomes an atom, and graph edges are physical blockade constraints for engineered exact unit-disk designs, or a 2D approximation to the semantic graph for natural texts. Three contributions follow. First, we introduce rigidity rho, a metric for how unique a book's structural backbone is -- distinguishing Marguerite de Navarre's Heptameron (rigid, twelve-nouvelle hard core) from Boethius (fully fungible, every chapter substitutable). Second, we invert the pipeline: rather than extracting a graph from existing prose, we pick a target graph the hardware encodes natively, and write a book whose structure matches it. The twenty-nine texts written this way, collected under the name QOuLiPo, extend the OuLiPo tradition to graph-topological constraints and, together with the eight natural texts, form a benchmark distribution against which neutral-atom hardware can be tracked as it scales. Third, we run both natural and engineered texts on Pasqal's FRESNEL processor up to one hundred atoms; engineered texts reach high approximation ratios, the cleanest instances returning the exact backbone. A cloud-accessible quantum machine plus an agentic coding environment now lets a single investigator run this pipeline end-to-end. What is reported is an application layer, not a speedup -- humanistic instances ready to load onto neutral-atom processors as they scale, already complementing classical text analysis. The Digital Humanities community has a stake in building familiarity with this hardware now: the engineered-corpus design choices made today fix the benchmark distribution future hardware will be measured against.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic communications</t>
+        </is>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Multi-Agent</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:29.237712+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>arxiv:2605.12500v1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SenseNova-U1: Unifying Multimodal Understanding and Generation with NEO-unify Architecture</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Haiwen Diao; Penghao Wu; Hanming Deng; Jiahao Wang; Shihao Bai; Silei Wu; Weichen Fan; Wenjie Ye; Wenwen Tong; Xiangyu Fan; Yan Li; Yubo Wang; Zhijie Cao; Zhiqian Lin; Zhitao Yang; Zhongang Cai; Yuwei Niu; Yue Zhu; Bo Liu; Chengguang Lv; Haojia Yu; Haozhe Xie; Hongli Wang; Jianan Fan; Jiaqi Li; Jiefan Lu; Jingcheng Ni; Junxiang Xu; Kaihuan Liang; Lianqiang Shi; Linjun Dai; Linyan Wang; Oscar Qian; Peng Gao; Pengfei Liu; Qingping Sun; Rui Shen; Ruisi Wang; Shengnan Ma; Shuang Yang; Siyi Xie; Siying Li; Tianbo Zhong; Xiangli Kong; Xuanke Shi; Yang Gao; Yongqiang Yao; Yves Wang; Zhengqi Bai; Zhengyu Lin; Zixin Yin; Wenxiu Sun; Ruihao Gong; Quan Wang; Lewei Lu; Lei Yang; Ziwei Liu; Dahua Lin</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2605.12500v1</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.12500v1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.12500v1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Recent large vision-language models (VLMs) remain fundamentally constrained by a persistent dichotomy: understanding and generation are treated as distinct problems, leading to fragmented architectures, cascaded pipelines, and misaligned representation spaces. We argue that this divide is not merely an engineering artifact, but a structural limitation that hinders the emergence of native multimodal intelligence. Hence, we introduce SenseNova-U1, a native unified multimodal paradigm built upon NEO-unify, in which understanding and generation evolve as synergistic views of a single underlying process. We launch two native unified variants, SenseNova-U1-8B-MoT and SenseNova-U1-A3B-MoT, built on dense (8B) and mixture-of-experts (30B-A3B) understanding baselines, respectively. Designed from first principles, they rival top-tier understanding-only VLMs across text understanding, vision-language perception, knowledge reasoning, agentic decision-making, and spatial intelligence. Meanwhile, they deliver strong semantic consistency and visual fidelity, excelling in conventional or knowledge-intensive any-to-image (X2I) synthesis, complex text-rich infographic generation, and interleaved vision-language generation, with or without think patterns. Beyond performance, we show detailed model design, data preprocessing, pre-/post-training, and inference strategies to support community research. Last but not least, preliminary evidence demonstrates that our models extend beyond perception and generation, performing strongly in vision-language-action (VLA) and world model (WM) scenarios. This points toward a broader roadmap where models do not translate between modalities, but think and act across them in a native manner. Multimodal AI is no longer about connecting separate systems, but about building a unified one and trusting the necessary capabilities to emerge from within.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic communications</t>
+        </is>
+      </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>生成</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:29.237916+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7117395041</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Technology-Enhanced Writing Pedagogy for EFL Learners: A Multi-Study Dissertation on Practice, Effectiveness, and Teacher Perceptions</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Xiao Lin</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>eScholarship (California Digital Library)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://escholarship.org/uc/item/1bf8j2r7</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://escholarship.org/content/qt1bf8j2r7/qt1bf8j2r7.pdf</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>English academic writing is a critical yet challenging skill for learners in English as a Foreign Language (EFL) contexts. The rapid integration of digital tools, accelerated by the COVID-19 pandemic, has transformed writing instruction; however, evidence of its pedagogical effectiveness remains fragmented and often overlooks teacher perceptions and genre-specific impacts. This three-study dissertation addresses these gaps by investigating the role of digital tools in EFL writing instruction within the EFL higher education context, employing a multi-method approach to triangulate evidence from student outcomes, meta-analytic synthesis, and teacher experiences.Study 1 conducted a classroom experiment with 111 Chinese undergraduates, comparing infographic-based pre-writing to traditional outlining. Results showed that infographic creation significantly improved summary-writing quality, source use, and self-efficacy, but not opinion writing, highlighting the genre-sensitive nature of tool effectiveness.Study 2 synthesized 17 experimental and quasi-experimental studies (N = 1,085) through a meta-analysis. It found a statistically significant, moderate overall effect favoring web-based collaborative writing (WBCW) over non-technological collaboration on writing quality&amp;nbsp;(Hedges’ *g* = 0.51). Moderator analyses indicated that training was a significant factor enhancing outcomes.Study 3 explored the perceptions of seven Chinese university writing instructors through qualitative interviews. Grounded in the TPACK framework, the findings revealed that while digital tools are deeply embedded in instruction, their use is shaped by teachers' knowledge, institutional support, and access. Teachers exhibited cautious and limited integration of emerging Generative Artificial Intelligence (GenAI) tools due to concerns over academic integrity and a lack of institutional guidance.Collectively, the findings demonstrate that technology enhances EFL academic writing most effectively when tools are aligned with genre demands, collaboration is scaffolded by design and training, and implementation is supported by teacher knowledge and institutional context. The dissertation concludes by advocating for a situated, tool-genre-task alignment perspective in future research and practice, moving beyond technocentric adoption to support equitable and effective writing instruction in diverse EFL settings.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic communications; goal-oriented communication; semantic-aware communication</t>
+        </is>
+      </c>
+      <c r="M35" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>生成</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:32.830203+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>arxiv:2605.12449v1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LychSim: A Controllable and Interactive Simulation Framework for Vision Research</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wufei Ma; Chloe Wang; Siyi Chen; Jiawei Peng; Patrick Li; Alan Yuille</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2605.12449v1</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.12449v1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.12449v1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>While self-supervised pretraining has reduced vision systems' reliance on synthetic data, simulation remains an indispensable tool for closed-loop optimization and rigorous out-of-distribution (OOD) evaluation. However, modern simulation platforms often present steep technical barriers, requiring extensive expertise in computer graphics and game development. In this work, we present LychSim, a highly controllable and interactive simulation framework built upon Unreal Engine 5 to bridge this gap. LychSim is built around three key designs: (1) a streamlined Python API that abstracts away underlying engine complexities; (2) a procedural data pipeline capable of generating diverse, high-fidelity environments with varying out-of-distribution (OOD) visual challenges, paired with rich 2D and 3D ground truths; and (3) a native integration of the Model Context Protocol (MCP) that transforms the simulator into a dynamic, closed-loop playground for reasoning agentic LLMs. We further annotate scene-level procedural rules and object-level pose alignments to enable semantically aligned 3D ground truths and automated scene modification. We demonstrate LychSim's capability across multiple downstream applications, including serving as a synthetic data engine, powering reinforcement learning-based adversarial examiners, and facilitating interactive, language-driven scene layout generation. To benefit the broader vision community, LychSim will be made publicly available, including full source code and various data annotations.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>semantic communications</t>
+        </is>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>生成</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:38.966067+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7148225585</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>From Computer to AI Communications: Toward Secure and Efficient Protocol</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Limos, Oussama, Habachi</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>HAL (Le Centre pour la Communication Scientifique Directe)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05574059</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05574059v1/document</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>International audience</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>semantic communications; semantic transmission; semantic channel coding</t>
+        </is>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>传输</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:42.235914+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>arxiv:2605.08439v1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Can Language Models Identify Side Effects of Breast Cancer Radiation Treatments?</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Natalie Seah; Danielle S. Bitterman; Daphna Spiegel; Thomas Hartvigsen</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2605.08439v1</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.08439v1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.08439v1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Accurately communicating the side effects of cancer treatments to cancer survivors is critical, particularly in settings such as informed consent, where clinicians must clearly and comprehensively convey potential treatment toxicities. However, this task remains challenging due to clinical knowledge deficits about adverse treatment effects and fragmentation across electronic health record (EHR) systems. Large language models (LLMs) have the potential to assist in this task, though their reliability in oncology survivorship contexts remains poorly understood. We present a deployment-oriented stress-testing framework for evaluating LLM-generated radiation side effect lists in breast cancer treatment and survivorship care. Using 21 breast cancer patient profiles, we construct paired patient clinical scenarios that differ only in radiotherapy regimens to evaluate seven instruction-tuned LLMs under multiple prompting regimes. We then compare LLM outputs to a clinician-curated reference derived from informed consent documents at two major academic medical centers and developed by a team including more than seven breast radiation oncologists. The reference maps radiation dose-fractionation, fields, and locations to associated toxicities, broken down by frequency and temporal onset. Across models, we reveal sensitivity to minor documentation changes, trade-offs between precision and recall, and systematic under-recall of rare and long-term side effects. When used alone, constraints on the number of side effects generated reduce precision, and grounding outputs in clinician-curated side effect lists substantially improves reliability and robustness. These findings highlight important limitations of LLM use in oncology and suggest practical design choices for safer and more informative survivorship-focused applications.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M38" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:58.613038+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>arxiv:2604.27933v1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Synthetic Biological Intelligence: System-Level Abstractions and Adaptive Bio-Digital Interaction</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Martin Schottlender; Pengjie Zhou; Veronika Volkova; Fatima Rani; Ruifeng Zheng; Juan A. Cabrera; Frank H. P. Fitzek; Pit Hofmann</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2604.27933v1</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2604.27933v1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2604.27933v1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Concurrent advances across fields such as organoid technology, Microelectrode Arrays (MEAs), neuromorphic computing, and machine learning have given rise to a groundbreaking research paradigm: Synthetic Biological Intelligence (SBI). SBI refers to engineered systems in which living Biological Neural Networks (BNNs) are interfaced with hardware and software to perform task-oriented information processing in a closed loop. This cutting-edge technology, while still in its infancy, has the potential to deliver highly efficient performance across both computing capabilities and energy consumption. The early stage of this field underscores the need for reliable multi-scale and cross-domain interaction interfaces to support applications in robotics, biomedicine, signal processing, and neuroscience research. The hitherto lack of commercially available SBI platforms has slowed the development, as the conditions to produce a testbed are expensive and cumbersome. The introduction of standardized, platform- and cloud-integrated BNNs has been a crucial catalyst for the scientific community, improving the accessibility of SBI and leading the way to further developments. In this survey, we summarize the innovations that contributed to the emergence of SBI and the first testbed interfaces that enabled its embodiment. This work reframes SBI as a bio-digital interaction system and introduces a unified protocol across encoding, decoding, system engineering, and benchmarking.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M39" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>任务导向通信</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>综述</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:58.613379+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7159911741</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>The Synthetic Persona Fallacy in HCI-Q Methodology</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Lucas Anastasiou; Anna De Liddo</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Open Research Online (The Open University)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://oro.open.ac.uk/view/person/la4227.html&gt;</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Designing platforms for multi-cultural and multilingual political deliberation requires a deep understanding of citizens' subjective viewpoints and potential points of friction. While Q-methodology is a robust statistical tool for uncovering these qualitative archetypes (recurring patterns of users' behaviours, motivations, or attitudes), its manual execution is highly resource-intensive. This paper investigates whether Large Language Models (LLMs) can automate Q-methodology by acting as demographically grounded ``Synthetic Citizens''. Grounded in the context of MultiPoD - a European initiative building cross-cultural citizen assemblies - we designed a policy scenario, and used it to collect baseline concourse and Q-sort data from human crowdworkers. Subsequently we tasked LLM-driven ``Synthetic Users'', prompted with matching demographic profiles, to perform the same tasks. Through a comparative Factor Analysis, we evaluated the statistical correlation between human and AI-generated viewpoints. Evaluating the algorithmic fidelity between human crowdworkers (N=62) and simulated AI agents, we found a profound lack of structural correspondence. Rather than replicating human viewpoint pluralism, synthetic users exhibited severe variance collapse, defaulting to a rigid, homogeneous consensus. Furthermore, LLMs displayed distinct "normative amplification'' and "coherence biases'', failing to simulate the human's relational and emotional motivations. Consequently, we argue that LLMs cannot safely replace human subjectivity in qualitative design research. Instead, we propose re-conceptualizing synthetic users as a ``sterile baseline'' within a subjectivity wind tunnel: a tool where human deviations from the AI's predictable consensus serve to actively pinpoint the real cultural, emotional, and sociotechnical friction in deliberative systems.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>semantic-aware communication</t>
+        </is>
+      </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>LLM / Agent 辅助语义通信</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:18:27.426097+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7134108658</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Governing Epistemic Risk in Large Language Model Use for Art History and Art Criticism Instruction: A Policy Analysis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Yuke Meng</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Open MIND</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10.17613/h0576-dh350</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://pub.respai.de/articles/1-1/3ymeng.html</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://pub.respai.de/articles/1-1/is1-3.pdf</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>The integration of large language models (LLMs) into higher education has proceeded faster than the development of discipline-sensitive governance. This gap is especially consequential in art history and art criticism instruction, where learning depends not only on factual accuracy but also on source fidelity, context reconstruction, interpretive plurality, and accountable judgment. This article develops a policy-centered analysis of the epistemic risks posed by LLM use in these domains. Drawing on international governance instruments and policy guidance from UNESCO, the OECD, NIST, and the European Union, as well as recent scholarship on hallucination, bias, automation, academic integrity, and higher education governance, the article argues that the distinctive epistemic structure of art-historical and critical inquiry makes these subjects vulnerable to a specific cluster of harms: fabricated attributions and references, canon-reinforcing bias, decontextualized summaries, interpretive flattening, and the outsourcing of judgment to systems whose outputs carry an unwarranted aura of authority. Existing higher-education policies on generative artificial intelligence often remain overly generic, framing risk in terms of plagiarism or disclosure while failing to address the epistemic conditions of disciplines organized around contested interpretation, visual evidence, and historically situated argument. In response, the article proposes a governance framework for art history and art criticism instruction organized around six principles: task classification by epistemic sensitivity; evidence-traceability requirements; assessment redesign to privilege documented reasoning; mandatory disclosure as pedagogical metadata rather than merely as compliance; procurement and tool approval standards for educational uses; and procedural safeguards to protect students from biased detection and opaque sanctions. The article concludes that policy for LLM use in art education should move beyond permissive tool adoption or blanket prohibition toward an institutional model of epistemic stewardship.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>semantic-aware communication</t>
+        </is>
+      </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>分类/识别</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:18:27.426184+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7153964182</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Toward a culturally situated perspective: Rethinking the role of AI in intangible cultural heritage pattern creation</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Xiaojing Yuan; Xiang Yuan; Sanyi Wang; Hao Li; Mengzhi He; Duoduo Zhang; Nick Bryan-Kinns</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>University of the Arts London Research Online (University of the Arts London)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://ualresearchonline.arts.ac.uk/view/creators/Yuan=3AXiaojing=3A=3A.html&gt;</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Research on generative artificial intelligence (GenAI) in cultural design has primarily focused on generative control and creative efficiency, often overlooking the misalignment between AI task definition and cultural creation. This study explores how GenAI can be culturally adapted within traditional pattern-making practices. Using an ethnographically informed generative probe, field experiments were conducted in the Huayao cross- stitch community, which practices a form of Chinese intangible cultural heritage. The findings reveal how cultural practitioners negotiate creative logic and cultural judgment when collaborating with AI, identifying four key orientations: liveliness, locality, creation-in-progress, and community creativity. Building on these insights, the paper redefines AI’s role as a generative reflexive actor and introduces the perspective of Culturally Situated Task Definition (CSTD) to explain how cultural tasks are redefined through the mutual shaping of technology and practice, advancing an understanding of the mechanisms underlying AI’s cultural adaptation and meaning co-construction.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>semantic transmission</t>
+        </is>
+      </c>
+      <c r="M42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:19:38.895209+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7160974116</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Covert Scrambling to the Edge in Tshangla: An Analysis of &lt;em&gt;Wh-&lt;/em&gt; In-Situ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tshering Y Dorji</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>CUNY Academic Works (City University of New York)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://academicworks.cuny.edu/gc_etds/6680</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://academicworks.cuny.edu/context/gc_etds/article/7886/viewcontent/tdorji_MA_thesis_manuscript_FINAL.pdf</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>This thesis investigates the syntactic derivation of wh- in-situ constructions in Tshangla, an understudied Tibeto-Burman language of Bhutan. Argument wh-items can remain in-situ in islands—including sentential subjects, adjunct clauses, relative clauses, and coordinate structures—while projecting their scope to the matrix level. This island-insensitivity for certain wh-items suggests a lack of movement in the narrow syntax, yet diagnostic tests, including crossover effects, reconstruction effects, and parasitic gap licensing, provide compelling evidence for a movement-based account. I propose an analysis involving covert LF scrambling to the left edge of an island clause. This movement is driven by semantic requirements to type-shift the clause from a proposition to a set of propositions. Once at the edge, the wh-item establishes an indirect dependency with the Q particle ya in the matrix clause, which functions as a scope marker. I also explore possible explanations for the asymmetry in kinds of wh-phrases that demonstrate island sensitivity. Beyond the analytic objectives, this thesis contributes to the typology of question formation by demonstrating a scope-taking strategy that differs from those in other well-studied wh-in-situ languages.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>semantic transmission</t>
+        </is>
+      </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:19:38.895281+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7109581480</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Wikidata and LiLa for Latin: Enabling Interoperability and Access to Inflected Forms and Corpus Attestations</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Lindemann, David; Pellegrini, Matteo; Mambrini, Francesco; Passarotti, Marco Carlo</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Zenodo (CERN European Organization for Nuclear Research)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>10.5281/zenodo.17839302</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.17839302</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.17839302</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>This paper presents an approach to integrating Latin inflected forms and corpus attestations within a Linked Open Data (LOD) framework, enhancing interoperability between Wikidata and the LiLa knowledge base. Building on the PrinParLat lexicon of Latin verb principal parts, we generate the complete set of inflected forms for over 8,000 verbs, encoded as RDF in a dedicated Wikibase instance. These forms are linked to the Index Thomisticus Treebank (ITTB), whose morphologically annotated tokens are related to corresponding forms based on segmental identity, lemma alignment, and mapped morphological features. Our generation and linking process achieves over 95% coverage of ITTB verbal tokens, demonstrating the robustness of our pipeline even for Medieval Latin data. By aligning Paralex, Wikidata, and LiLa ontologies, we ensure semantic interoperability and facilitate future integration into Wikidata. Beyond Latin, this workflow provides a reproducible model for linking inflectional paradigms and corpus attestations in other languages.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>semantic encoding</t>
+        </is>
+      </c>
+      <c r="M44" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>生成</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:20:30.523156+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7137737438</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>The evolving regulation of religious behavior in the public sector: the case of the reserve obligation in a senegalese military corps</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ndiaga Seye; Amadou Sidy Aly Ba; Hugo Gaillard; Michael Westlake</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Cairn.info</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/journal-gestion-et-management-public-2024-5-page-1d?lang=en</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/article/E_GMP_PR1_0034/pdf?lang=en</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>This research examines the regulation of religious expression in the public and military context of Senegal. Our aim is to understand the process through which religious expression at work (REW) is regulated and how it is shaped by both implicit and explicit rules in an African context that remains underexplored in the literature. Social Regulation Theory (SRT) is used as the analytical framework to study the regulation of REW. We adopted a qualitative methodology, conducting twenty-four (24) semi-structured interviews with firefighters. The findings first reveal a penetration of religious expression into military services, driven by divergent perceptions of control rules, which remain nonetheless constraining. Secondly, the results highlight the existence of a more or less intense joint regulation throughout military life, influenced by contextual factors. These findings offer managerial implications for military services operating in secular contexts where the population is predominantly religious – a societal configuration that is increasingly prevalent. Finally, this study provides new insights into how national context shapes the regulation of religious expression at work and the associated managerial behaviors, responding to a gap identified in the literature.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic-aware communication</t>
+        </is>
+      </c>
+      <c r="M45" t="b">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:32.829673+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7137680744</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>New Public Management in cultural fields? Professionalization, commodification and “expertization” in French contemporary poetry</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sébastien Dubois</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Cairn.info</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/journal-gestion-et-management-public-2024-5-page-1p?lang=en</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>New Public Management (NPM) has been the subject of academic study in many sectors, but much less so in the cultural sector. This article focuses on poetry, the actions of public authorities in a largely publicly funded sector, and the consequences of these actions on the status and social life of poets. Using a qualitative methodology based on interviews, this article shows that NPM has influenced cultural policy in poetry by creating a quasi-market of literary activities and sources of income for poets (readings, performances, workshops, scholarships and grants, and residencies) where demand from public authorities (state, local authorities, multiple autonomous actors financed by public funds) for “artistic services” provides work opportunities to poets in the form of short, non-renewable contracts. This transforms poets into “service providers’, obtaining contracts from multiple organisations, often with cross-financing. Every market requires regulation: in the case of poetry, a “proceduralizing” process accompanies the growth of this quasi-market. However, one of the specificities of culture is that the state chooses without really choosing, because a democratic state does not possess the legitimacy to impose or choose according to aesthetic or political preference. Contemporary state patronage of poetry, therefore, is ambiguous: it requires poets to perform artistic and even social work for which they are paid, albeit privately. The work is literally more social because more and more contracts offered to poets include a social component where culture is considered a means of educating and/or repairing social bonds. This system ends up commodifying poetry, changing poets into “service providers” and “sales reps” of their own work, propounding a double process of professionalization and “expertisation”. Faced with the impossibility of choosing, the State appeals directly and indirectly to “poetry experts”, sometimes directly soliciting poetry actors in the selection procedures, and more generally by relying on the reputation of poets which has been manufactured in the world of poetry by the poetry actors themselves. The article illustrates how a cultural policy, inspired by the principles of NPM, can change the status of actors – here artists – even going against the representations of the artists and managers who manage this quasi-market. Paradoxically, the actors do not want this commo-dification despite it being the fruit of an organisational system linked to transformations in public action and management.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M46" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:15:02.018078+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7137764721</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>The Social and Solidarity Economy and Public Authorities in South Korea : Constructing a Complementary Relationship</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Éric Bidet; Casper Hendrik Claassen; Junki Kim</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Cairn.info</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/journal-gestion-et-management-public-2024-5-page-1aa?lang=en</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/article/E_GMP_PR1_0029/pdf?lang=en</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>This article examines the historical trajectory of the Social and Solidarity Economy (SSE) in South Korea, where it has experienced spectacular development over the past fifteen years, analyzing it through the lens of its relationship with public authorities. The longitudinal analysis conducted for the period 1910-2020 is based on a mixed methodology that combines often incomplete and heterogeneous descriptive statistics, documentary analysis, examination of institutional documents, thematic interviews, and case studies. It also mobilizes the theoretical framework of social origins theory established by Salamon and Anheier (1998) and the typology of relationships between the nonprofit sector and public authorities proposed by Young (2000) to demonstrate that the typical relationship between SSE and public authorities follows fluctuating models specific to each historical period and tends toward a complementary relationship marked by reciprocal influences and growing SSE autonomy. We thus observe the establishment of a hybrid bottom up and top down process through which the SSE tends to become not only a service provider but also a partner to public authorities in the formulation of public policy. The complementary relationship between SSE and public authorities creates a coupling/decoupling dynamic that combines the advantages of SSE agility (Room, 2011) and the intervention capacity of the developmental state (Woo-Cumings, 1999).</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>goal-oriented communication</t>
+        </is>
+      </c>
+      <c r="M47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Hybrid Classical + Neural Coding</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:16:13.434023+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7137489039</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Business Model Innovation among Startups and Its Future Research Trends: A Systematic Review and Bibliometric Analysis of Relevant Literature</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Salsabil Thabti; Waleed Omri; Audrey Bécuwe; Abdelwahed Omri</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Cairn.info</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/revue-journal-of-innovation-economics-2025-0-page-I200?lang=en</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>This paper explores the potential of renewable energy technologies and smart grids to drive a transformative shift in the energy landscape. Drawing inspiration from the concept of technological revolutions, the paper examines historical examples of techno-economic paradigms and their reliance on abundant and low-cost energy resources. It highlights the current emergence of low-carbon energy generation technologies, such as wind, solar, and hydropower, and their integration into the digital technoeconomic paradigm. The paper emphasizes the co-evolution of green and digital transition processes and their potential to create diversified energy networks. It investigates the connections between technological revolutions, renewable energy sources, and smart grids, suggesting that these elements will shape the future energy transition.JEL Codes: O13, O33, O44</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>semantic communication</t>
+        </is>
+      </c>
+      <c r="M48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>综述类论文</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>综述</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:32.829957+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7160677245</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Defying the Catholic Secondary School Enrollment Decline: A Case Study Exploring Strategic Enrollment Management Practices in an All-Boys Catholic High School</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Traci A Koval</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Seton Hall University eRepository (Seton Hall University)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://scholarship.shu.edu/dissertations/4446</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://scholarship.shu.edu/cgi/viewcontent.cgi?article=4446&amp;context=dissertations</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Catholic secondary schools in the United States continue to face persistent enrollment decline, closures, and consolidations, creating an urgent need for sustainable and mission-centered strategies. This qualitative case study examined Hillcrest Catholic High School, an all-boys Catholic secondary school in the Mideast region, as a best-practice model for enrollment resilience. Guided by Strategic Enrollment Management (SEM) Theory, the study explored how SEM principles were operationalized across eight pillars: mission and branding, institutional strategy, culture and belonging, programs and outcomes, family engagement and retention, tuition and financial strategy, marketing and recruitment, and selection and onboarding. Data were collected through interviews, focus groups, observations, and artifact analysis. Findings revealed that Hillcrest Catholic High School sustained enrollment growth through the intentional integration of Catholic mission with institutional strategy and daily practice. Clear and consistent mission-driven branding strengthened market positioning and differentiated the school in a competitive educational marketplace; stakeholder ownership fostered a culture of belonging; academic and co-curricular programming aligned with family expectations and postsecondary outcomes; transparent tuition and financial messaging enhanced trust and accessibility; and relational recruitment and onboarding practices supported both enrollment and retention. The findings suggest that Strategic Enrollment Management (SEM), when integrated with and grounded in Catholic identity, functions as a comprehensive and holistic framework for sustaining and strengthening enrollment in Catholic secondary schools while preserving institutional mission.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>task-oriented communication; goal-oriented communication</t>
+        </is>
+      </c>
+      <c r="M49" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>LLM / Agent 辅助语义通信</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:15:02.018337+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7159750554</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Revising the Role of Minors and Their Participation in Their End-of-Life Care: An Argument for a Shared Decision-Making Model Rooted in Pediatric Patients’ Decision-Making Capacity</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Taylor Talcott</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Seton Hall University eRepository (Seton Hall University)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://scholarship.shu.edu/student_scholarship/1744</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://scholarship.shu.edu/cgi/viewcontent.cgi?article=2740&amp;context=student_scholarship</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>You undergo the transplant, but in the weeks following, your body begins to shut down, rejecting the new marrow.You are plagued with intense, unwavering joint aches, and it is becoming harder to breathe by the minute.Every breath you take becomes harder and harder to hold onto, your body screaming for more air, and you become afraid of what will happen when you cannot catch your breath anymore.Your doctor informs you and your parents that without a ventilator, you will soon be unable to breathe on your own, necessitating a move to the ICU.Fearing the worst, you beg your parents not to send you there because you do not want to die there.Your parents, with their hearts shattering with every pained look of yours, turn their back and ask the doctor to do whatever it takes to save you.You go to the ICU and connect to the ventilator, which hurts more than you thought, even with the sedatives you take.With every ragged breath, you feel your lungs being forcefully pushed open, and as days pass, you develop ulcerations, both in your throat from the tube and over your back from being confined to bed for so long.Days, weeks, maybe even months pass, and you feel the world slipping away to the point that you remain barely aware of your surroundings beyond the pain and can no longer communicate.You hear your family's wails and hushed conversations, whispering in your ear that they will never give up on you, but you are powerless to respond.Days drift by with little distinction, and all you can do is lie and wait -those fleeting glimpses of sunlight through a window or the voice of a parent becoming the highlights of your existence.Eventually, days slip into weeks, and then months; finally, you die alone in the ICU at night after visiting hours are over, scared, in pain, and completely helpless.A. Why Minors' Participation in their End-of-Life Decision-Making, is Necessary of whom need end-of-life hospital care, either acutely or long term.End of life (EOL) decisions in the context of terminal or chronic, life-limiting illnesses are medical decisions that have possible lifeshortening effects, and they precede 40% of deaths of both adults and minors. 2 Moreover, as medical technologies and understandings have advanced, child mortality due to common illnesses has precipitously dropped; yet, of the survivors, many now face life-long limiting conditions or illness-related complications which can cause considerable discomfort and poor quality of life -prompting potential end-of-life (EOL) discussions. 3 Given improvements in medical technologies and resuscitation, children are likely to live longer when afflicted by many injuries or illnesses, but the improvement in survival does not necessarily correspond to an increase in the quality of life. 4Depending on the medical context, the continuation of life-sustaining treatment may not always be within a child's best interest, despite the general discomfort shared by both many parents and physicians regarding the withdrawal or withholding of life-sustaining care in young patients.Even when physicians and parents determine it is within the child's best interest to withdraw life-sustaining treatment (LST) and any non-palliative care, minor patients rarely have a substantial say in the trajectory of their end-of-life care.While doctors may consider a child's stated preferences, especially if that patient is a teenager, children are rarely viewed as "real" decisionmakers, meaning that their views will be overridden by a parent or the physician should they disagree. 5 Legal and professional standards governing end-of-life care for minor patients must prioritize informed consent of and participation of the patients themselves.As explicated by the</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>task-oriented communication; goal-oriented communication</t>
+        </is>
+      </c>
+      <c r="M50" t="b">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:15:02.018554+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7143585285</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>The Ethical and Legal Complexities of Regulating Companion AI Chatbots</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sue Anne Teo; S. P. Mann; Paul Jurcys</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Lund University Publications (Lund University)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/record/01283f65-6f24-4249-8cf5-94c73b1d0685</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/search/files/244841408/Ethical_and_Legal_complexities_of_regulating_companion_chatbots.pdf</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Companion AI chatbots are increasingly used to provide friendship, emotional support, and quasi-romantic relationships, with reported benefits for loneliness and mental health. At the same time, recent suicides and other serious harms allegedly linked to such systems expose gaps in existing ethical and legal frameworks. This article interrogates these gaps through four lenses: anthropomorphism, emotional AI, emergent vulnerabilities, and mismatched legal taxonomies. First, we show how companion chatbots rely on anthropomorphic cues, creating a regulatory tension between enabling meaningful connection and avoiding deception, over-trust, and unhealthy dependency. Second, we argue that current debates on ‘emotional AI’ over-emphasise emotion recognition and under-theorise emulated empathy, where chatbots solicit self-disclosure and perform care in ways that can both support and undermine users’ autonomy. Third, we introduce the notion of emergent vulnerabilities that arise through ongoing interactions, rather than being fully specifiable ex ante, challenging legal regimes that presuppose stable vulnerability categories. Fourth, we show how instruments such as the EU AI Act misalign with the temporality, intentionality, and relational character of companion AI harms. Stepping back from these lenses, we argue for the development of a dedicated theory of harm for companion AI and propose ‘intimacy capitalism’ as a conceptual framework for analysing how firms monetise, shape, and potentially exploit digitally mediated intimate relations.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M51" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>分类/识别</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:15:02.018613+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7154662464</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Setting Up Living Labs for Water Reuse in Water-Stressed Social-Hydrological Systems</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Olivier Barreteau; Justine Bassoul; Magali Gerino; Claire Albasi; Stéphanie Bost</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Cairn.info</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/revue-journal-of-innovation-economics-2025-0-page-I205?lang=en</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/article/E_JIE_PR2_0205/pdf?lang=en</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Water reuse is a potential solution for adapting to the impacts of global change on water availability. Given its highly contingent and controversial nature, this requires a participatory research process. Here, we describe the experimental design and implementation of co-research, based on a hybridisation of Living Labs and Science Shops methodologies. This approach enables the involvement of all stakeholder categories – policy makers, private businesses, civil society organisations and academics – from the research programme development phase onwards. We report on the experimental implementation of this approach in six Living Labs in southern France, focusing on water reuse. We characterise these Living Labs according to existing environmental Living Labs approaches. The process yields grounded new knowledge about water reuse and strengthens social links for exploring water-related issues. JEL Codes: O350, Q250, Q280</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M52" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>IoT / 边缘智能</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Hybrid Classical + Neural Coding</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:15:02.018656+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7137754632</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Le New Public Management dans la culture ? Professionnalisation, marchandisation et « expertisation » dans la poésie contemporaine</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Sébastien Dubois</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Cairn.info</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/revue-gestion-et-management-public-2024-5-page-1p?lang=fr</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/article/GMP_PR1_0026/pdf?lang=fr</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>New Public Management (NPM) has been the subject of academic study in many sectors, but much less so in the cultural sector. This article focuses on poetry, the actions of public authorities in a largely publicly funded sector, and the consequences of these actions on the status and social life of poets. Using a qualitative methodology based on interviews, this article shows that NPM has influenced cultural policy in poetry by creating a quasi-market of literary activities and sources of income for poets (readings, performances, workshops, scholarships and grants, and residencies) where demand from public authorities (state, local authorities, multiple autonomous actors financed by public funds) for “artistic services” provides work opportunities to poets in the form of short, non-renewable contracts. This transforms poets into “service providers’, obtaining contracts from multiple organisations, often with cross-financing. Every market requires regulation: in the case of poetry, a “proceduralizing” process accompanies the growth of this quasi-market. However, one of the specificities of culture is that the state chooses without really choosing, because a democratic state does not possess the legitimacy to impose or choose according to aesthetic or political preference. Contemporary state patronage of poetry, therefore, is ambiguous: it requires poets to perform artistic and even social work for which they are paid, albeit privately. The work is literally more social because more and more contracts offered to poets include a social component where culture is considered a means of educating and/or repairing social bonds. This system ends up commodifying poetry, changing poets into “service providers” and “sales reps” of their own work, propounding a double process of professionalization and “expertisation”. Faced with the impossibility of choosing, the State appeals directly and indirectly to “poetry experts”, sometimes directly soliciting poetry actors in the selection procedures, and more generally by relying on the reputation of poets which has been manufactured in the world of poetry by the poetry actors themselves. The article illustrates how a cultural policy, inspired by the principles of NPM, can change the status of actors – here artists – even going against the representations of the artists and managers who manage this quasi-market. Paradoxically, the actors do not want this commodification despite it being the fruit of an organisational system linked to transformations in public action and management.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>task-oriented communication</t>
+        </is>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:15:02.018750+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7116109956</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Contested urbanisms: The politics of heritage and housing in Jakarta’s kampungs</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Binte Masron, Irna Nurlina</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>BIROn (Birkbeck, University of London)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>10.18743/pub.00056687</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7116109956</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://eprints.bbk.ac.uk/id/eprint/56687/1/Binte%20Masron%20I%2C%20final%20thesis%20for%20library.pdf</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Do heritage-making projects resist or advance gentrification in Southeast Asia? Like other Global South cities, contested urbanisms chequer Jakarta’s postcolonial urban landscape. Competing ideas about urban development manifest in various ways of seeing and producing the city, as demonstrated by evictions, revitalisation projects, and informal housing. Increased evictions of urban villages (urban kampungs) between 2013 and 2018 in Jakarta saw growing grassroots heritage movements as part of a spectrum of resistance to top-down urban management by state and private sector actors who also stake their claims on what ‘heritage’ is. These tensions amongst the political projects of various actors led me to ask: how do heritage-making projects of/by urban villages affect housing conditions in Jakarta, with reference to gentrification-led displacement? Using ethnographic methods and thematic analysis, I delve into the constructions of heritage, the impact of heritage-making on housing security for residents, and the broader political impact of heritage-making from above and below in Jakarta’s Kota Tua and two of its kampungs, Luar Batang and Pekojan. I argue that the dominant heritage constructions in Kota Tua demonstrate a top-down logic that emphasises infrastructure and the built environment with strong private sector presence, which impact the kampungs in varied ways. Findings showed that top-down heritage-making demonstrates higher likelihood of driving gentrification through the commodification of space, prioritising capital and material values. Residents and their advocates employ heritage-making from below in various forms to reclaim their place in the city as they face various forms of displacement, with unanticipated consequences. The processes of heritage-making from above and below reveal the connections and disjunctures between different authorities which subaltern actors work through, producing new politics that contest or entrench existing conditions. The findings contribute to the theorising of the politics of gentrification in heritage and urban studies, and a deeper understanding of Jakarta’s Old Town.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>task-oriented communication; goal-oriented communication</t>
+        </is>
+      </c>
+      <c r="M54" t="b">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:15:02.018828+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7137753545</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Économie sociale et solidaire et pouvoirs publics en Corée du Sud : la construction d’une relation de complémentarité</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Éric Bidet; Casper Hendrik Claassen; Junki Kim</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Cairn.info</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/revue-gestion-et-management-public-2026-0-page-1?lang=fr</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/article/GMP_PR1_0029/pdf?lang=fr</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Cet article revient sur la trajectoire historique de l’ESS en Corée du Sud, où elle a connu un développement spectaculaire depuis une quinzaine d’années, et en propose une lecture au prisme de sa relation avec les pouvoirs publics. L’analyse longitudinale menée sur la période 1910-2020 repose sur une méthodologie mixte qui combine ici statistiques descriptives souvent incomplètes et hétérogènes, analyse documentaire, examen de documents institutionnels, entretiens thématiques et études de cas. Elle mobilise par ailleurs le cadre théorique de la théorie des origines sociales établi par Salamon et Anheier (1998) et la typologie des relations entre secteur but non lucratif et pouvoirs publics proposée par Young (2000) pour montrer que la relation-type entre l’ESS et les pouvoirs publics relève de modèles fluctuants propres à chaque époque historique et tend vers une relation de complémentarité marquée par des influences réciproques et une autonomie croissante de l’ESS. On observe ainsi la mise en place d’un processus hybride ascendant et descendant où l’ESS tend à devenir, non seulement un prestataire, mais un partenaire des pouvoirs publics et de la définition des politiques publiques. La relation de complémentarité entre ESS et pouvoirs publics s’accompagne d’une dynamique de type couplage/découplage qui combine les avantages de l’agilité de l’ESS (Room, 2011) et de la capacité d’intervention de l’État développeur (Woo-Cumings, 1999).</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>goal-oriented communication</t>
+        </is>
+      </c>
+      <c r="M55" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Hybrid Classical + Neural Coding</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:16:13.434444+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7155586310</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Combining Foresight Narratives and Serious Games to Codevelop Adaptive Water Management Pathways</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Nina Graveline; Juliette Le Gallo; Alexandre Alix; Marta Debolini; David Dorchies; Katrin Erdlenbruch; Sébastien Loubier</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Cairn.info</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/revue-journal-of-innovation-economics-2025-0-page-I207?lang=en</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>In the Mediterranean area, climate change threatens both farming and water resources. The need for methods to support reflection and dialogue on transformational adaptation strategies is urgent. We propose and demonstrate an innovative approach, co-constructing pathways for climate change adaptation and water management by combining (i) participative scenario building and (ii) a serious game. While the first explores the combination of exogenous driving forces on the agricultural system consistent with SSPs at regional level, the serious game allows us to explore the co-evolution of land and water use and related policies at the farm level. Results confirm that land use can vary greatly in a medium-term horizon. Our approach helps to envision the role of land use and diversification in future water demand under climate change. The results show that the effect of land use changes on water demand is much higher than the effect of climate scenarios. JEL Codes: B4, B5, O3, Q1, Q2</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>goal-oriented communication</t>
+        </is>
+      </c>
+      <c r="M56" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:16:13.434491+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7137520389</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nature et tensions du contrôle de gestion environnemental dans les collectivités locales</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Christophe Maurel; Christophe Favoreu</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Cairn.info</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/revue-gestion-et-management-public-2026-0-page-1d?lang=fr</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://shs.cairn.info/article/GMP_PR1_0033/pdf?lang=fr</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Cette recherche exploratoire vise à caractériser d’une part le concept de contrôle de gestion environnemental (CGE) à travers les pratiques qui le sous-tendent et, d’autre part, les tensions associées à celui-ci et à l’implantation de ces pratiques au sein des organisations publiques. En effet, bien que suscitant un intérêt grandissant au sein du secteur public le CGE semble faire face à des difficultés techniques et de gouvernance. Une grille d’analyse des outils de gestion et la théorie des paradoxes organisationnels sont retenues pour répondre à notre problématique de caractérisation dans le secteur public local des pratiques de CGE et des tensions associées. Différentes communes ont été mobilisées afin d’explorer et de caractériser les premières expériences d’implantation du CGE. Nos résultats permettent de caractériser à la fois les outils utilisés mais aussi les tensions générées entre les objectifs poursuivis au niveau de la gestion des ressources, du dialogue avec l’environnement socio-économique et de l’orientation des comportements.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>goal-oriented communication</t>
+        </is>
+      </c>
+      <c r="M57" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:16:13.434535+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>arxiv:2605.14913v1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Representative Attention For Vision Transformers</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Yuntong Li; Hainuo Wang; Hengxing Liu; Mingjia Li; Xiaojie Guo</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2605.14913v1</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>http://arxiv.org/abs/2605.14913v1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2605.14913v1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Linear attention has emerged as a promising direction for scaling Vision Transformers beyond the quadratic cost of dense self-attention. A prevalent strategy is to compress spatial tokens into a compact set of intermediate proxies that mediate global information exchange. However, existing methods typically derive these proxy tokens from predefined spatial layouts, causing token compression to remain anchored to image coordinates rather than the semantic organization of visual content. To overcome this limitation, we propose Representative Attention (RPAttention), a linear global attention mechanism that performs token compression directly in representation space. Instead of constructing intermediate tokens from fixed spatial partitions, it dynamically forms a compact set of learned representative tokens to enable semantically related regions to communicate regardless of their spatial distance, by following a lightweight Gather-Interact-Distribute paradigm. Spatial tokens are first softly gathered into representative tokens through competitive similarity-based routing. The representatives then perform global interaction within a compact latent space, before broadcasting the refined information back to all spatial tokens via query-driven cross-attention. Via replacing coordinate-driven aggregation with representation-driven compression, RPAttention preserves global receptive fields while adaptively aligning token communication with the content structure of each input.RPAttention reduces the dominant token interaction complexity from quadratic to linear scaling with respect to the number of spatial tokens, while maintaining expressive global context modeling. Extensive experiments across diverse vision transformer backbones on image classification, object detection, and semantic segmentation demonstrate the effectiveness of our design.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic communications</t>
+        </is>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>图像语义通信</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>分类/识别</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:29.237495+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7121465138</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>DYNAMICS OF PORTFOLIO ASSESSMENT STRATEGY IN EVALUATING THE ENGLISH LANGUAGE SKILLS FOR PUPILS WITH HEARING IMPAIRMENTS IN FAKO DIVISION, SOUTH WEST REGION OF CAMEROON</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ngenwie Emilia Tanyie; Therese Mungah Shalo Tchombe</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Zenodo (CERN European Organization for Nuclear Research)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>10.5281/zenodo.18206766</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://ubueajournals.org/index.php/IJDIEH/article/view/28</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://ubueajournals.org/index.php/IJDIEH/article/download/28/24</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>This study examined the impact of portfolio assessment on evaluating the English language skills of pupils with hearing impairment in Fako Division, Cameroon. Portfolio assessment, as an informal and learner-centred approach, was explored within the framework of inclusive education, where traditional assessment methods often fail to adequately reflect the abilities of learners with hearing loss. The research utilised a quasi-experimental design involving pupils with hearing impairment in selected inclusive primary schools. Data were gathered through English language tests, classroom observations, and interviews with parents, teachers, head teachers, and the divisional delegate. Quantitative data were analysed using descriptive statistics, t-tests, and regression analysis, while qualitative data underwent thematic analysis. The results indicated that pupils subjected to portfolio assessment performed significantly better in English language skills than those assessed through conventional methods. Statistical analysis (SPSS t-tests and regression) showed that pupils assessed via portfolios scored notably higher on post-tests (portfolio group mean=12.78 versus control=11.14; t(38)=2.919, p&lt;.05). Regression analysis demonstrated that portfolio use was a strong predictor of language improvement (β=0.336, p&lt;.001). Classroom observations and interview findings further revealed that portfolio assessment encouraged ongoing learning, increased learner engagement, self-reflection, and heightened teacher awareness of individual progress. The study concludes that portfolio assessment is an effective method for evaluating the English language skills of pupils with hearing impairment and recommends its systematic adoption within inclusive classroom practice.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic-aware communication</t>
+        </is>
+      </c>
+      <c r="M59" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:32.830026+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7126357041</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Accessing primary care following the Affordable Care Act : a qualitative study of low-income women’s experiences in urban California</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>A. I. Gilchrist; Paula Holland; Faraz Ahmed</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Lancaster EPrints (Lancaster University)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7126357041</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Background The 2010 Affordable Care Act (ACA) led to Medicaid expansion, which expanded eligibility to low-income individuals below 138% of the federal poverty level in 41 states and Washington, DC. In California, over one-third of state residents are covered by Medicaid (Medi-Cal) insurance. Despite the 2014 Medicaid expansion in California, many individuals remain uninsured. Low-income women, in particular, face significant primary care access challenges due to socioeconomic status, education, and minority/disability status. This qualitative study aimed to explore the experiences of low-income women seeking and accessing primary care services following the ACA’s Medicaid expansion in California in an urban setting. Methods In-depth, semi-structured interviews were conducted with 18 women in Northern California (2021–2022). Data analysis employed Braun and Clarke’s reflexive thematic analysis using a deductive approach. Levesque’s conceptual framework of access to healthcare guided the coding and interpretation. Results The experiences of low-income women with primary care access post Medicaid expansion in an urban California setting were shaped by the complex interplay of individual demand-side factors and health system supply-side factors, and structural determinants. Levesque’s framework highlights how individual factors (self-efficacy, health literacy, social support, and affordable insurance) interact with health system factors (geographic accessibility, availability and accommodation of services, and provider-patient relationships) to shape low-income women’s experiences. However, Levesque’s framework could be strengthened by incorporating macro-level structural factors (socioeconomic, political factors, and health policies) as these profoundly influence healthcare access. Conclusions These findings provide a strong foundation for policymakers and practitioners to develop multi-level policies and interventions to address the ongoing barriers that urban low-income women encounter when accessing primary care following the ACA’s Medicaid expansion. These findings are also relevant for other U.S. states and international settings that face similar challenges stemming from healthcare inequalities, including a lack of universal healthcare.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>semantic communication</t>
+        </is>
+      </c>
+      <c r="M60" t="b">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:32.830109+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7130910808</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Reconstruction and Renaissance of Dongbei China:A Multimodal Metaphor Analysis of New Media on Harbin</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Amily; id_orcid 0000-0001-5583-9442 Wang Guenier; Amily; id_orcid 0000-0001-5583-9442 Wang Guenier</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Research Explorer (The University of Manchester)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://research.manchester.ac.uk/en/publications/02ba2ca7-0a6a-45f6-8e18-8cf3c7218f17</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://pure.manchester.ac.uk/ws/files/1813360438/_2025_.pdf</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic communications; semantic-aware communication; semantic transmission; semantic encoding; semantic channel coding</t>
+        </is>
+      </c>
+      <c r="M61" t="b">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>多模态语义通信</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Multimodal</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:32.830216+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W4414932055</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Universal Audio Generation</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Antoine Laurent; Sameer Khurana; Anthony Larcher; Dominik Klement; Mickaël Rouvier; Santiago Cuervo; Adel Moumen; Antonio Almudévar; Haroun Elleuch; Peter Gazdik; Dominik Boboš; Juraj Novosad; Hugo Riguidel; Salima Mdhaffar; Radim Kudla; Zili Huang; Elric Zhang; Laura Cristina Alonzo Canul; Ricard Marxer; Tuan Nguyen</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>HAL (Le Centre pour la Communication Scientifique Directe)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05110014</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05110014v1/document</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>This report describe the research done during the third ESPERANTO/JSALT workshop from the 10th June 2024 to the 2nd of August 2024.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic-aware communication; semantic encoding</t>
+        </is>
+      </c>
+      <c r="M62" t="b">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>语音语义通信</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>生成</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Speech</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:32.830256+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7140350618</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Building a reflexive space for scientific dialogue through the digital reconstruction case of the Palais Stoclet dining room</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Flavius-Teofil Neaga; Denis Derycke; David Lo Buglio</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Dépôt institutionnel de l'Université libre de Bruxelles (Université Libre de Bruxelles)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>http://hdl.handle.net/2013/ULB-DIPOT:oai:dipot.ulb.ac.be:2013/404568</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>http://hdl.handle.net/2013/ULB-DIPOT:oai:dipot.ulb.ac.be:2013/404568</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Digital three-dimensional reconstructions of architectural heritage have become increasingly used as research tools, yet their visually coherent representations often conceal the interpretive processes, uncertainties, and evidential gaps underlying their production. This paper proposes a method for visualising evidential proximity, defined as the distance between the reconstructed geometry and the documented sources that support it, within three-dimensional architectural restitution models. The method is based on the systematic evaluation of heterogeneous historical sources according to their integration modes (transposition, interpretation, and extrapolation), across multiple analytical aspects of the architectural elements. These evaluations are represented directly within the 3D model using a source-based visual encoding approach implemented through native tools in Blender, an open-source 3D modeling software. Its application is demonstrated through the digital reconstruction of the dining room of the Palais Stoclet, a UNESCO World Heritage building that is inaccessible for direct survey and only known through documentary sources. Embedding interpretive metadata within the model itself frames 3D reconstruction as a reflexive space for scientific exchange, contributing to transparency, critical evaluation, and the projection of reconstruction hypotheses across time.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>semantic communication; semantic encoding</t>
+        </is>
+      </c>
+      <c r="M63" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>图像语义通信</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>综述</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:32.830470+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7126005415</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mind the Gap: Connecting Protocol Representations in Squirrel</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>David Baelde; Stéphanie Delaune; Julia Gabet; Clément Hérouard</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>HAL (Le Centre pour la Communication Scientifique Directe)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05013723v1/document</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05013723/document</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>International audience</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>semantic communications; semantic encoding; semantic channel coding</t>
+        </is>
+      </c>
+      <c r="M64" t="b">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:42.235743+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7128652737</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Multi-Taxonomy Vulnerability Classification with Hierarchically Finetuned Language Models</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Franco Terranova; Sana Rekbi; Abdelkader Lahmadi; Isabelle Chrisment</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>HAL (Le Centre pour la Communication Scientifique Directe)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05500820</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05500820/document</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>International audience</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>semantic communications; semantic-aware communication</t>
+        </is>
+      </c>
+      <c r="M65" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>分类/识别</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:42.235758+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7128888790</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deep Learning-Based Data Hiding Technique for Medical Images</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hadjer SAIDI</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>University of Biskra Theses Repository (University of Biskra)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7128888790</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>http://thesis.univ-biskra.dz/7149/1/These_Saidi_Hadjer%20.pdf</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>This thesis introduces novel deep learning-based frameworks for secure medical image steganography, addressing the critical challenge of protecting sensitive patient information while preserving diagnostic quality. Medical images present unique security requirements due to their dual nature: containing both critical visual data for diagnosis and sensitive patient metadata, which conventional steganographic techniques do not adequately address. Our work presents two complementary approaches to this challenge. First, we develop a Mask-RCNN based framework that intelligently identifies diagnostically insignificant regions within medical images for strategic data embedding. By combining this regionaware detection with Discrete Cosine Transform (DCT) embedding in the frequency domain, our method achieves remarkable imperceptibility with Peak Signal-to-Noise Ratio (PSNR) values exceeding 115 dB while maintaining high payload capacity. Second, we propose a clinical quality-aware convolutional neural network architecture that leverages an encoder-decoder framework for end-to-end steganography. This approach employs parallel processing paths with scaled residual learning to embed secret medical images within cover images while preserving diagnostic features. Extensive experimentation across multiple medical imaging modalities (CT, MRI) from datasets including MIDRC-RICORD-1B, and IQ-OTH/NCCD, demonstrates that our method achieves a good trade-off between payload and imperceptibility. The frameworks developed in this thesis achieve an optimal balance between embedding capacity, imperceptibility, and robust secret recovery, providing healthcare institutions with effective tools for safeguarding patient privacy while maintaining the integrity of medical diagnostics. This work significantly advances the field of medical image security and establishes a foundation for future innovations in secure healthcare information systems.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>semantic communications; semantic-aware communication; semantic transmission; semantic channel coding</t>
+        </is>
+      </c>
+      <c r="M66" t="b">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>图像语义通信</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>CNN / DeepJSCC</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:42.235822+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7153309785</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Knowing your weaknesses is your greatest strength:Mapping CVE to CWE by leveraging CWE Hierarchy and LLMs</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Stefano; id_orcid 0009-0009-9778-4019 Simonetto; Ronan Oostveen; Thijs van Ede; Peter Bosch; Willem Jonker; Stefano; id_orcid 0009-0009-9778-4019 Simonetto</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>University of Twente Research Information</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>10.1145/3779208.3785376</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://research.utwente.nl/en/publications/f6a774fb-9d09-4c1a-8b29-cb7377fb3411</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://ris.utwente.nl/ws/files/527526035/asiaccs_knowing_weakness.pdf</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Effective defense against threat actors requires that security professionals accurately identify the underlying weaknesses associated with common vulnerabilities and exposures (CVEs). This under standing is crucial for deploying appropriate defensive mechanisms and prioritizing remediation efforts. However, manually mapping CVEs to common weakness enumerations (CWEs) has become increasingly impractical due to the rapid increase of new CVEs and&lt;br/&gt;the extensive, complex CWE taxonomy. In 2025, the number of CVEs awaiting analysis exceeded 25,000.&lt;br/&gt;&lt;br/&gt;To automate the mapping between CVEs and CWEs, we propose to leverage two insights. To harness the power of large language models, we first fine-tune different language models to perform this mapping based on the vulnerability-to-weakness relation. Second, we propose a supervised framework leveraging the hierarchical structure of CWEs, where we first categorize vulnerabilities into&lt;br/&gt;broad CWE classes (e.g., Injection, Buffer Overflow), which helps capture high-level patterns, and then utilizes specialized subnet works to distinguish fine-grained differences within each class.&lt;br/&gt;&lt;br/&gt;Evaluated on a benchmarkthat covers 95% of all CVEs associated with a CWE, our approach improves F1-score by 5% over the best prior supervised method, demonstrating the value of combining model fine-tuning with hierarchy-aware classification.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>semantic communications; semantic-aware communication</t>
+        </is>
+      </c>
+      <c r="M67" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>LLM / Agent 辅助语义通信</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>分类/识别</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:42.235876+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7140019487</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CLEAR: Scheduling of Multi-model Mobile Workloads on Chiplet Edge Platforms</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chetna Singhal; Matteo Mendula; Francesco Malandrino; Marco Levorato; Carla Fabiana Chiasserini</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>HAL (Le Centre pour la Communication Scientifique Directe)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05555466</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>International audience</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>semantic communications; semantic transmission; semantic channel coding</t>
+        </is>
+      </c>
+      <c r="M68" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>IoT / 边缘智能</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:42.235891+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7151152401</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Intelligent Network System: Service Provisioning Using AI-Agents</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Chetna Singhal; yassine Hadjadj-Aoul</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>HAL (Le Centre pour la Communication Scientifique Directe)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05577132</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05577132v1/document</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>International audience</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>semantic communications</t>
+        </is>
+      </c>
+      <c r="M69" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>LLM / Agent 辅助语义通信</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Multi-Agent</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:42.235903+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7119831517</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>DroidHunter : une détection robuste basée sur la vision contre les logiciels malveillants Android obfusqués</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Victoire Nganfang; Simon Queyrut; David M. Bromberg; Valerio Schiavoni; Djob Mvondo; Vianney Kengne Tchendji</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>HAL (Le Centre pour la Communication Scientifique Directe)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>10.1145/3779208.3785386</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05419946</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05419946v1/document</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>International audience</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>semantic communications; semantic channel coding</t>
+        </is>
+      </c>
+      <c r="M70" t="b">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:14:42.235932+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7134999412</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Platforming threatoric on TikTok : racial‑religious fear during Malaysia’s 15th general election</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Siti Nurnadilla Mohamad Jamil</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Lancaster EPrints (Lancaster University)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7134999412</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://eprints.lancs.ac.uk/id/eprint/235854/1/Platforming_Threatoric_on_TikTok-_snmj-revised-cleaned-AAM.pdf</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>This paper examines how TikTok shaped the production and circulation of threatoric, the affective and discursive staging of racial and religious threat, during Malaysia’s 15th General Election (GE15). Drawing on Proximisation Theory (PT) and Social Media Critical Discourse Studies (SM-CDS), it analyses 60 publicly accessible TikTok videos collected between 5 and 24 November 2022 that mobilise ethnoreligious anxieties, frequently invoking the May 13, 1969 riots to frame political opposition as imminent existential danger. Moving beyond content-centred analysis, the paper approaches threatoric as a platformed genre organised through observable platform formats and techno-semiotic resources. The analysis identifies four recurring patterns: affective-sonic staging, epistemic claims to evidentiality, platformed polyvocal legitimation, and interactional and translational amplification that intensify spatial, temporal, and axiological proximisation in multimodal form. Synthesising these patterns, the paper specifies eight platform affordances through which ideological fear is rendered familiar, morally saturated, and presented as epistemically self-evident within the sampled dataset. It argues that GE15 TikTok content does not constitute an ideological rupture but a platformed rearticulation of enduring ethnonationalist anxieties under conditions of platformed politics.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>semantic transmission</t>
+        </is>
+      </c>
+      <c r="M71" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>视频语义通信</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>生成</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:19:38.895061+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7140254711</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Time Lapse: Deducting Claims and Expenses Under Section 2053</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>McCouch, Grayson M.P.</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>eYLS (Yale Law School)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://scholarlycommons.law.hofstra.edu/acteclj/vol50/iss3/3</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://scholarlycommons.law.hofstra.edu/context/acteclj/article/1302/viewcontent/Time_Lapse.pdf</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>semantic transmission</t>
+        </is>
+      </c>
+      <c r="M72" t="b">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:19:38.895231+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7160971463</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Twitteratura: Digital Social Reading and Active Reception of Literary Texts in the Context of Italian Contemporary Literature</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Iuri Moscardi</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>CUNY Academic Works (City University of New York)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://academicworks.cuny.edu/gc_etds/6667</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://academicworks.cuny.edu/context/gc_etds/article/7833/viewcontent/IuriMoscardi_DISSERTATION_def_rev.pdf</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>This dissertation explores Digital Social Reading (DSR) as a novel mode of literary engagement, focusing on the Italian project Twitteratura, a series of social reading experiments conducted on Twitter (2012–2016) and later on the Betwyll app. The research situates Twitteratura within the intersection of Reader-Response Theory, Digital Humanities, Reception Studies, and Sociology of Literature, demonstrating how digital environments reshape the act of reading and interpretation. Through detailed analyses of four DSR projects centered on major twentieth-century Italian authors—Cesare Pavese, Pier Paolo Pasolini, Italo Calvino, and Natalia Ginzburg—this dissertation argues that Twitteratura provides a concrete, data-rich demonstration of Wolfgang Iser’s reader-response theory in action, reconfiguring the relationship between author, text, and reader in the digital age. The study begins by positioning Twitteratura within the broader history of literary theory and digital culture by drawing on Wolfgang Iser’s conception of reading as an active process that completes the aesthetic object, and on Hans Robert Jauss’s notion of reception as a historical, collective event. From these theoretical foundations, the study examines how digital platforms have expanded the field of literary participation, producing new forms of social hermeneutics that merge interpretation, creativity, and community-building. This framework is further informed by Digital Humanities scholarship emphasizing collaboration, openness, and the democratization of knowledge, as well as by Media and Platform Studies addressing Twitter’s transformation from a microblogging platform into a participatory social medium. The dissertation addresses three main research questions: (1) How can Twitteratura’s practices of digital social reading exemplify and expand reader-response theory? (2) What interpretive strategies do readers employ in DSR environments, and how do these relate to genre, medium, and authorial presence? (3) How can computational and qualitative methods combine to analyze literary reception in digital networks? To answer these questions, the adopted approach combined close reading, digital text analysis, and reception study. Each DSR project is analyzed through a corpus of tweets or twlls, categorized according to five interpretive strategies: quotation, summary, comment, identification, and remake. These categories are then compared across the four case studies to assess how readers’ engagement shifts with text type, platform affordances, and community dynamics. The four case studies—#LunaFalò, #Corsari, #Invisibili, and #CaroMichele—trace the evolution of Twitteratura from its inception to its later development on Betwyll. Each represents a different mode of literary engagement. #LunaFalò (2012) tested the viability of DSR as a collective interpretive method, while #Corsari (2013) foregrounded critical discourse around Pasolini’s civic and political ideas. #Invisibili (2013) demonstrated creative intertextuality through collective rewriting inspired by Calvino’s Invisible Cities. Finally, #CaroMichele (2016), hosted on Betwyll, emphasized educational and pedagogical applications of DSR, showing how classroom participation reshapes traditional reading practices. The comparative analysis of these projects yields several key findings. First, DSR practices reveal that reader-response theory not only survives but thrives in the digital age, as readers publicly perform the interpretive acts Iser theorized as internal and private. The microtextual format of Twitter and Betwyll externalizes the cognitive and emotional dimensions of reading, making them visible, archivable, and analyzable. Second, the genre and medium of the original text strongly shape readers’ engagement strategies. Narrative texts encourage empathetic identification, while argumentative or poetic texts promote commentary and creative reappropriation. The shift from Twitter to Betwyll further reveals how platform design—character limits, threading, visibility—affects interpretive expression. Third, Twitteratura demonstrates that digital environments can democratize literary culture, turning reading into a collective and creative act that blurs the boundary between scholarship and popular participation. Ultimately, this dissertation argues that Digital Social Reading is not a technological curiosity but a humanistic phenomenon—one that reaffirms the centrality of the reader in the literary experience. It bridges the gap between solitary and communal reading, between aesthetic reflection and social interaction, and between traditional literary criticism and digital humanities methodologies. By analyzing how Italian readers have collectively reimagined their literary heritage through Twitter and Betwyll, this work illuminates broader transformations in global literary culture: from passive consumption to participatory creation, from national canons to transnational communities of interpretation.</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>semantic transmission</t>
+        </is>
+      </c>
+      <c r="M73" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:19:38.895493+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7157522334</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Le COVID-19 est-il vraiment derrière nous ? Comprendre et accompagner les difficultés cognitives et fonctionnelles dans le COVID Long : apports d'un essai randomisé contrôlé</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Carmen Cabello Fernandez</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Open Repository and Bibliography (University of Liège)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://orbi.uliege.be/handle/2268/344444</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://orbi.uliege.be/handle/2268/344444</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>semantic transmission</t>
+        </is>
+      </c>
+      <c r="M74" t="b">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:19:38.895513+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7128571704</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Debugging debugging information using dynamic call trees</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>J. Ryan Stinnett; Stephen Kell</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Research Portal (King's College London)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://kclpure.kcl.ac.uk/portal/en/publications/f82a4449-b7f2-4977-88a4-94dc35b8459c</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://kclpure.kcl.ac.uk/ws/files/366852635/paper.pdf</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Debugging tools rely on compiler-generated metadata to present a source-language view, but current compilers often throw away or corrupt debugging information in optimised programs.Attempts to test debugging information are confounded by ad-hoc limitations of the debug info formats and a lack of clarity on whether the compiler or the format is to blame for any given loss.Adopting the "residual program" conceptual view of debug info, we conduct a study of the quality of debugging information in respect of the source-level dynamic call trees it can recover.We compare the trees recovered from optimised and unoptimised versions of the same program, producing a classification of the observed divergences.For each class, we analyse whether format or compiler is to blame and identify specific ways to address these defects.We also validate our classification across a larger collection of well-known codebases.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>semantic encoding</t>
+        </is>
+      </c>
+      <c r="M75" t="b">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>分类/识别</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:20:30.523251+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7128875661</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Grasping by interconnection : can robust and adaptive grasping emerge from minimal object information?</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Julien Vanderheyden; Guillaume Drion; Pierre Sacré; Fulvio Forni</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ORBi (University of Liège)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://orbi.uliege.be/handle/2268/341416</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://orbi.uliege.be/bitstream/2268/341416/1/IROS_VM_grasping.pdf</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>This paper investigates whether robust and adaptive dexterous grasping can emerge from minimal object information by modeling grasping as a dynamic interconnection between the robot and a simplified object representation. Instead of relying on precise object models or large-scale data-driven training, objects are approximated using coarse geometric primitives (sphere, cylinder, and box), each associated with a canonical grasp type from human grasp taxonomies. Grasp execution is formulated within the Virtual Model Control (VMC) framework, where virtual springs and dampers mechanically couple a virtual hand to a virtual object, allowing grasp motions to emerge naturally from the coupled dynamics rather than from predefined trajectories. Structured stiffness distributions and adaptive damping profiles promote coordinated, human-like finger closure while mitigating object ejection during transient phases. The approach is implemented on a Shadow Dexterous Hand and evaluated through robustness and generalization experiments under geometric and pose uncertainties, as well as on a diverse set of everyday objects. Results support the hypothesis that reliable dexterous grasping can arise from minimal yet structured object representations combined with dynamic object–robot interconnection.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>semantic encoding</t>
+        </is>
+      </c>
+      <c r="M76" t="b">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:20:30.523308+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7160500182</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Retrieval Augmented Generation Using Multimodal Large Language Models for Real-Time Knowledge-Grounded Question Answering</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Dr. K. Sujatha</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Open MIND</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>10.5281/zenodo.20068396</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://www.ijama.in/papers?paper=Retrieval+Augmented+Generation+Using+Multimodal+Large+Language+Models+for+Real-Time+Knowledge-Grounded+Question+Answering</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://ijama.in/admin/a/uploads/pdf/1778148494_IJAMA - April 2026.pdf</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>The exponential growth of heterogeneous digital information across structured and unstructured repositories presents a critical challenge for large language models (LLMs): the inability to access and reason over dynamically evolving knowledge without costly model retraining. This paper introduces a comprehensive Retrieval Augmented Generation (RAG) framework that integrates multimodal large language models (MLLMs) with real-time, knowledge-grounded question answering systems. The proposed architecture — MultiRAG — combines a dense bi-encoder retrieval backbone with a cross-modal fusion module capable of jointly indexing and retrieving text, images, tables, and structured data. Retrieved multimodal evidence is processed by a vision-language model (VLM) serving as the generative backbone, conditioned on retrieved context through a novel cross-attention grounding mechanism that attenuates hallucination by enforcing faithfulness constraints at the token level. Experiments conducted on four benchmark datasets — Natural Questions, WebQA, MultiModalQA, and a custom real-time knowledge update benchmark (RKUB-2024) — demonstrate that MultiRAG achieves 87.3% Exact Match on open-domain QA, 91.4% answer faithfulness score, and 6.7× reduction in hallucination rate compared to vanilla LLM baselines. Real-time knowledge ingestion pipeline latency averages 340 ms per document, supporting continuous knowledge grounding without model fine-tuning. The system reduces hallucination by 82% over standard LLM deployment and outperforms all retrieval-augmented baselines by 4.2–9.8 percentage points across evaluation metrics</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>semantic encoding</t>
+        </is>
+      </c>
+      <c r="M77" t="b">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>生成</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:20:30.523456+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7142561823</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Crash Course in Digital Scholarly Editions - Learning What to Do and How to Do It with Open Source and Semi-Automatic Tools: DH2026 Workshop</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Floriane Chiffoleau</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>HAL (Le Centre pour la Communication Scientifique Directe)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05564494</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05564494v1/file/Crash%20Course%20in%20Digital%20Scholarly%20Editions%20-%20Learning%20What%20to%20Do%20and%20How%20to%20Do%20It%20with%20Open%20Source%20and%20Semi-Automatic%20Tools.pdf</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>International audience</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>semantic encoding</t>
+        </is>
+      </c>
+      <c r="M78" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:20:30.523471+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7142584203</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>"You Get the Best of Both Worlds" - Making the Association for the Blinds' Cultural Heritage Available for Researchers and Blind People</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Floriane Chiffoleau; C. Roussel; Marion Chottin; Glenn Roe; Motasem Alrahabi</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>HAL (Le Centre pour la Communication Scientifique Directe)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05564504</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://hal.science/hal-05564504v1/file/%E2%80%9CYou%20Get%20the%20Best%20of%20Both%20Worlds%E2%80%9D%20%E2%80%93%20Making%20the%20Association%20for%20the%20Blinds%E2%80%99%20Cultural%20Heritage%20Available%20for%20Researchers%20and%20Blind%20People.pdf</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>International audience</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>semantic encoding</t>
+        </is>
+      </c>
+      <c r="M79" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:20:30.523489+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7128116870</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Neurolinguistic signatures of microvariation and language change : Individual production variability predicts morphosyntactic processing differences</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Jade J. Sandstedt; Maki Kubota; Merete Anderssen; Stig J. Helset; Björn Lundquist; Øystein Alexander Vangsnes; Jason Rothman</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Lancaster EPrints (Lancaster University)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://openalex.org/W7128116870</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>This study investigates the neurophysiological and behavioral effects of exposure to grammatical microvariation, focusing on the relationship between individual production patterns and on-line sentence processing. We examine a unique context of ongoing morphosyntactic change in Norwegian participial agreement, which gives rise to widespread, near-continuous variation in agreement marking across dialects and speakers. Event-related potentials (ERPs) were recorded from 156 participants drawn from two dialect regions with extensive inter- and intra-speaker variability, as they read sentences in standardized Norwegian Bokmål containing either invariant (control) or variable/changing (target) grammatical forms. Results show that both group-level dialect background and individual production frequencies modulate sentence processing. Participants from regions undergoing dialect change exhibit attenuated P600 effects and more gradient acceptability judgments, and neural sensitivity to participial agreement violations is continuously modulated by individual age and spoken agreement rates. These findings provide evidence that language processing is dynamically shaped by fine-grained individual differences in linguistic experience – including community-level exposure, personal production frequencies, and sociolinguistic positioning within ongoing grammatical change – and that even narrow between- and within-individual variation in dialectal grammar influences integration costs during standard language comprehension.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>semantic channel coding</t>
+        </is>
+      </c>
+      <c r="M80" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>未分类</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>未标注</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:21:37.635098+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>openalex:https://openalex.org/W7160007104</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Beyond Polarity: Continuous Affect-Enhanced Multimodal Aspect-Based Sentiment Classification</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ling-ang Meng; Tianyu Zhao; Dawei Song; Jingxu Cao; Youhui Zuo</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Open Research Online (The Open University)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>OpenAlex</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://oro.open.ac.uk/view/person/ds7946.html&gt;;</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Multimodal aspect-based sentiment classification (MABSC) requires aspect-level sentiment inference from textual–image data that jointly convey opinions. Yet most existing approaches primarily exploit discrete polarity patterns and generic visual embeddings, making them less effective when the affect is subtle, implicit, or expressed through imagery. In this work, we propose &lt;b&gt;&lt;i&gt;VADE&lt;/i&gt;&lt;/b&gt;, a Valence–Arousal–Dominance (&lt;b&gt;&lt;i&gt;VAD&lt;/i&gt;&lt;/b&gt;)-&lt;b&gt;&lt;i&gt;E&lt;/i&gt;&lt;/b&gt;nhanced MABSC framework that brings continuous VAD signals into multimodal sentiment reasoning and learns emotion-sensitive image representations. Specifically, we design a &lt;b&gt;VAD encoder&lt;/b&gt; to extract continuous affect cues from text for aspect-level sentiment reasoning. Furthermore, we fine-tune a CLIP-based image encoder on affect-enriched image–text pairs to obtain visual representations that are more sensitive to sentiment cues. To support the fine-tuning process, we construct an affect-enriched image–text dataset, &lt;b&gt;&lt;i&gt;Senti-COCO&lt;/i&gt;&lt;/b&gt;, by rewriting MSCOCO captions with a multimodal large language model, yielding large-scale image–text pairs with richer affective expressions. Experiments on two mainstream datasets, Twitter‑15 and Twitter‑17, show that &lt;b&gt;VADE&lt;/b&gt; achieves state-of-the-art performance, demonstrating the effectiveness of incorporating Valence, Arousal, and Dominance (VAD) signals for MABSC.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>semantic channel coding</t>
+        </is>
+      </c>
+      <c r="M81" t="b">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>文本语义通信</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Foundation Model / LLM</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>分类/识别</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>低相关性候选，需要人工复核</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>2026-05-15T12:21:37.635169+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X1"/>
+  <autoFilter ref="A1:X81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/weekly/semantic_communication_papers_2026-W20.xlsx
+++ b/outputs/weekly/semantic_communication_papers_2026-W20.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Optimization / Resource Allocation</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Autoencoder / DeepSC</t>
+          <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Autoencoder / DeepSC</t>
+          <t>Optimization / Resource Allocation</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Multi-Agent</t>
+          <t>Optimization / Resource Allocation</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Reinforcement Learning</t>
+          <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>未分类</t>
+          <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Multi-Agent</t>
+          <t>Information Theory / Semantic Coding</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">

--- a/outputs/weekly/semantic_communication_papers_2026-W20.xlsx
+++ b/outputs/weekly/semantic_communication_papers_2026-W20.xlsx
@@ -10,7 +10,7 @@
     <sheet name="papers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'papers'!$A$1:$X$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'papers'!$A$1:$Y$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -440,17 +440,18 @@
     <col width="42" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="42" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="42" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,65 +512,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>arxiv_comment</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>is_open_source</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>code_url</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>project_url</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>open_source_evidence</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>application_scenario</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>technical_framework</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>task_type</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>modality</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>relevance_score</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>curation_status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>last_checked_at</t>
         </is>
@@ -625,51 +631,52 @@
           <t>Despite significant advancements in communication systems, inherent limitations persist in providing reliable data transmission for emerging applications with massive data exchanges. Semantic communication offers promising solutions by extracting and transmitting meaningful information rather than raw bit sequences. However, it faces challenges from high mobility and dynamic channel conditions in wireless environments. In this paper, we design a ground-to-air network architecture that integrates a rotary-wing unmanned aerial vehicle (UAV) and ground terminals to maximize semantic transmission efficiency while maintaining low energy consumption. This approach leverages the high mobility of the UAV for flexible deployment and the data reduction capabilities of semantic communication. Therefore, we formulate a multi-objective optimization problem to simultaneously balance the total semantic transmission rate and the UAV propulsion energy consumption by jointly optimizing the UAV hovering position, semantic encoding lengths, and resource block (RB) allocation. The problem is complex, with mixed continuous and discrete variables, which necessitates an advanced optimization method. To address these challenges, we propose a novel greedy-enhanced adaptive multi-objective cellular genetic algorithm (GEAMOCell), which utilizes an adaptive neighborhood selection mechanism to balance exploration and exploitation, and employs a crowding-guided archive feedback mechanism to maintain population diversity. The simulation results demonstrate that the proposed GEAMOCell algorithm outperforms baseline algorithms in terms of convergence, semantic transmission rate, and energy efficiency.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>DeepSC</t>
         </is>
       </c>
-      <c r="M2" t="b">
+      <c r="N2" t="b">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>not_detected</t>
-        </is>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>source_error:papers_with_code;source_error:pdf_link_extract</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>6G / 无线通信</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Optimization / Resource Allocation</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>13.5</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844757+00:00</t>
         </is>
@@ -725,51 +732,52 @@
           <t>Semantic communication systems for goal-oriented transmission must protect task-relevant information not only through source compression but also via physical layer mapping. Existing approaches decouple constellation design and semantic encoding, exposing critical symbols to channel errors at the same rate as irrelevant ones. Contrary to this, in this paper, a joint semantic-physical layer framework is proposed, which is composed of a vector quantized-variational autoencoder that extracts discrete latent concepts, a semantic criticality indicator (SCI) that scores each concept by task relevance, and a deep reinforcement learning agent that dynamically selects the transmission subset based on instantaneous channel conditions. At the physical layer, a learned semantic-aware M -QAM constellation assigns symbol positions according to joint co-occurrence statistics and SCI scores, departing from the uniform spacing and Gray coding of standard M -QAM which minimizes average BER without regard for semantic content. We introduce a novel semantic symbol vulnerability (SSV) metric and a semantic protection probability (SPP) to quantify the exposure of task-critical symbols to decoding errors, and prove that any Gray-coded constellation is strictly suboptimal in SCI-Weighted SSV whenever the source exhibits non-uniform semantic importance and co-occurrence statistics. Simulation results demonstrate that the proposed constellation achieves near 100% SPP across modulation orders from 4-QAM to 1024-QAM versus 50% for standard constellations at high spectral efficiency, a 21:1 compression ratio with semantic quality above 0.9, generalizing across MNIST, Fashion-MNIST, and FSDD without modification.</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>semantic communication; semantic communications; task-oriented communication</t>
         </is>
       </c>
-      <c r="M3" t="b">
+      <c r="N3" t="b">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>not_detected</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>source_error:papers_with_code</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>任务导向通信</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>9.5</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>2026-05-15T12:14:29.237416+00:00</t>
         </is>
@@ -825,51 +833,52 @@
           <t>Semantic communication (SemCom) with learned encoder-decoder architectures enables end-to-end learning of compact task-oriented representations optimized for the wireless channel, reducing channel resources needed to convey task-relevant information and improving spectrum efficiency. This paper studies semantic image transmission over block Rayleigh fading with AWGN using a multi-task semantic autoencoder that jointly reconstructs images and predicts labels from the received waveform. The latent dimension (complex channel uses per source sample) serves as a cross-layer control variable governing semantic fidelity and channel resource usage. We characterize the resulting latency-task fidelity tradeoff: larger latent representations improve inference accuracy but increase service time, channel uses, and queueing delay. Building on this insight, we develop online semantic-rate controllers that adapt the latent dimension per update under a long-term semantic error constraint. A queue-aware drift-plus-penalty policy minimizes delay subject to an average semantic error cap, while a complementary age-aware policy minimizes time-average Age of Information (AoI). By adapting the semantic rate to congestion and fidelity requirements, the proposed framework improves spectrum utilization and enables timely semantic updates with significantly lower delay and AoI than fixed-rate baselines.</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>task-oriented communication</t>
         </is>
       </c>
-      <c r="M4" t="b">
+      <c r="N4" t="b">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>not_detected</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>source_error:papers_with_code</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>6G / 无线通信</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Optimization / Resource Allocation</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Image</t>
         </is>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>8</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>2026-05-15T12:14:58.613259+00:00</t>
         </is>
@@ -925,51 +934,52 @@
           <t>With the rapid development of intelligent services, communication objectives are shifting from humans to multi-agent (MA) systems. This transition necessitates new communication paradigms capable of supporting real-time perception, decision-making, and collaboration among agents. Semantic communication (SeC) focuses on the efficient transmission and accurate understanding of information “meaning” and is well-suited to meet the needs of Mas, such as collaborative perception, reasoning, and decision-making. However, the transmission of semantic information is still constrained by dynamic environments and the diversity of MA tasks. To address these challenges, this work proposes a COmparative learning Joint Optimal (COJO) SeC framework. This work makes three main contributions: first, it jointly optimizes the image reconstruction and classification functions designed for multi-task semantic objectives under different channel conditions, thereby improving the overall task performance of the system; second, based on input image features, compression ratio, task requirements, and channel conditions, an enhanced further compressor is designed, which obtains a training-based mask to significantly reduce the volume of transmitted data; finally, to prevent the loss of key semantic information in multi-task scenarios under channel constraints, it designs a task-driven end-to-end semantic communication training scheme.</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>DeepSC</t>
         </is>
       </c>
-      <c r="M5" t="b">
+      <c r="N5" t="b">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>not_detected</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>source_error:papers_with_code;source_error:pdf_link_extract</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>LLM / Agent 辅助语义通信</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Multi-Agent</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>分类/识别</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Image</t>
         </is>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>7.5</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844490+00:00</t>
         </is>
@@ -1025,51 +1035,52 @@
           <t>Semantic communication (SC) can achieve superior coding and transmission performance based on the knowledge contained in the semantic knowledge base (KB). However, conventional KBs consist of source KBs and channel KBs, which are often costly to obtain data and limited in data scale. Fortunately, large language models (LLMs) have recently emerged with extensive knowledge and generative capabilities. Therefore, this paper proposes an SC system with LLM-enabled knowledge base (SC-LMKB), which utilizes the generation ability of LLMs to significantly enrich the KB of SC systems. In particular, we first design an LLM-enabled generation mechanism with a prompt engineering strategy for source data generation (SDG) and a cross-attention alignment method for channel data generation (CDG). However, hallucinations from LLMs may cause semantic noise, thus degrading SC performance. To mitigate the hallucination issue, a cross-domain fusion codec (CDFC) framework with a hallucination filtering phase and a cross-domain fusion phase is then proposed for SDG. In particular, the first phase filters out new data generated by the LMKB irrelevant to the original data based on semantic similarity. Then, a cross-domain fusion phase is proposed, which fuses source data with LLM-generated data based on their semantic importance, thereby enhancing task performance. Besides, a joint training objective that combines cross-entropy loss and reconstruction loss is proposed to reduce the impact of hallucination on CDG. Experiment results on three cross-modality retrieval tasks demonstrate that the proposed SC-LMKB can achieve up to 72.6\% and 90.7\% performance gains compared to conventional SC systems and LLM-enabled SC systems, respectively.</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>DeepSC</t>
         </is>
       </c>
-      <c r="M6" t="b">
+      <c r="N6" t="b">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>not_detected</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>source_error:papers_with_code</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>LLM / Agent 辅助语义通信</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>Foundation Model / LLM</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>生成</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>7.5</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844921+00:00</t>
         </is>
@@ -1125,51 +1136,52 @@
           <t>This letter investigates the problem of energy efficient collaborative strategy for mobile embodied artificial intelligence network (MEAN) over wireless communication. In the considered model, the agents execute the tasks through collaboration, and they can switch between two operating modes based on the signal-to-noise ratio (SNR) and global collaboration. The dual-mode comprises the base station (BS)-assisted collaborative mode, in which agents make decisions through semantic communication with BS and then collaborate on tasks, and the local computing mode, in which the agents make decisions and execute tasks independently. Due to the dynamic wireless communication and flexible collaboration strategy, we jointly consider computation energy, communication energy, and task-execution energy with specific collaborative gains into a mixed-integer nonlinear programming (MINLP) optimization problem whose goal is to minimize the total system energy consumption. To solve it, we propose a lower-complexity enumeration algorithm: first, we get the optimal closed-form solution for semantic compression ratio and transmit power by proving the strict convexity. Second, we determine the scale of collaboration and the operating mode of each agent by a greedy sorting algorithm based on individual energy-saving potentials. Simulation results show that the proposed algorithm can significantly reduce the total energy consumption compared to benchmark schemes.</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>semantic communication; semantic communications</t>
         </is>
       </c>
-      <c r="M7" t="b">
+      <c r="N7" t="b">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>not_detected</t>
-        </is>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>source_error:papers_with_code</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>6G / 无线通信</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Optimization / Resource Allocation</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>7</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>2026-05-15T12:14:29.237651+00:00</t>
         </is>
@@ -1225,51 +1237,52 @@
           <t>This paper proposes a novel adaptive dual-path framework for covert semantic communication (SemCom), which integrates covert information transmission with task-oriented semantic coding. Unlike conventional covert communication methods that embed hidden messages through power-domain signal superposition, our framework embeds covert data within task-specific features via semantic-level intrinsic encoding. This new architecture introduces dual encoding paths with adaptive block selection: an Explicit path for public task execution and a Stego path that jointly encodes both public and covert information through contrastive representation alignment. A Gumbel-Softmax enabled adaptive path selection mechanism dynamically activates network blocks based on task require- ments. We formulate a multi-objective optimization framework that simultaneously ensures accurate semantic understanding and reliable covert transmission. We rigorously evaluate our framework's security against a powerful, independently trained attacker. Experimental results on the Cityscapes dataset demon- strate a state-of-the-art level of covertness: our method suppresses the attacker's detection accuracy to a near-random guessing level of 56.12%. This robust security is achieved while simultaneously maintaining superior performance on the primary semantic tasks compared to the baselines.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>task-oriented communication; DeepSC</t>
         </is>
       </c>
-      <c r="M8" t="b">
+      <c r="N8" t="b">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>not_detected</t>
-        </is>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>source_error:papers_with_code</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>任务导向通信</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2026-05-15T12:14:58.613325+00:00</t>
         </is>
@@ -1325,51 +1338,52 @@
           <t>Pinching-antennas systems (PASS) offer reconfigurable wireless channels via low-cost dielectric mediums by creating line-of-sight (LoS) communication links. Most of the existing PASS cover mechanisms of equal power pinching antennas for conventional bit-based communication, whereas flexible radiation control remains largely unexplored, particularly for heterogeneous semantic and bit users. In this paper, we investigate the performance of semantic communication (SC) using an adjustable radiation model over PASS, where the coupling strength between the dielectric waveguide and each pinching antenna is determined by the antenna-waveguide spacing. Specifically, the non-orthogonal multiple access (NOMA)-assisted heterogeneous users are served by multiple pinching antennas using spacing-controlled adjustable radiation ratios. Uunder this setting, we maximize the semantic spectral efficiency (SE) subject to the bit-user quality of service (QoS) requirement, successive interference cancellation (SIC) feasibility, and the minimum adjacent antennas spacing constraint. An alternating optimization (AO) approach optimizes users power allocation and positions of pinching antennas. Simulations demonstrate the effectiveness of the proportional power PASS model in providing higher semantic SE in different geometrical and numerical settings compared to conventional benchmark schemes.</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>DeepSC</t>
         </is>
       </c>
-      <c r="M9" t="b">
+      <c r="N9" t="b">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>not_detected</t>
-        </is>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>source_error:papers_with_code</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>6G / 无线通信</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>7</v>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844545+00:00</t>
         </is>
@@ -1425,51 +1439,52 @@
           <t>We investigate the performance of the pinching-antenna systems (PASS) for semantic communication (SC) in both single-waveguide and multi-waveguide scenarios, under the constraints of bit-user quality of service (QoS) and bit-to-semantic decoding order in a heterogeneous users downlink non-orthogonal multiple access (NOMA). Multiple pinching antennas in the single-waveguide scenario are at a minimum adjacent spacing required to prevent mutual coupling. An alternating optimization (AO)-based algorithm optimizes users power allocation coefficients and position of pinching antennas in the single-waveguide NOMA framework. For the multi-waveguide scenario, assuming adjacent waveguides at a sufficient lateral distance apart, the waveguides power allocation subproblem is solved using monotonic optimization and minorization-maximization (MM) approach. Specifically, a lower bound surrogate is iteratively maximized under the feasibility constraints such that a non-decreasing sequence of objective is obtained. Numerical results demonstrate that the NOMA based PASS exploiting SC offers higher semantic spectral efficiency (SE) while fulfilling the bit-user QoS requirement when compared to the considered conventional fixed antenna system. Notably, the multi-waveguide scenario becomes more beneficial for creating adjustable wireless channels in stringentconditions with higher bit-user QoS and wider coverage area requirements.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
         <is>
           <t>DeepSC</t>
         </is>
       </c>
-      <c r="M10" t="b">
+      <c r="N10" t="b">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>not_detected</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>source_error:papers_with_code</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>6G / 无线通信</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>7</v>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844853+00:00</t>
         </is>
@@ -1525,51 +1540,52 @@
           <t>The rapid growth of foundation model training and large-scale AI services has driven ground data centers toward unprecedented power densities, intensifying challenges in energy supply, cooling, and spatial scalability. Space Data Centers (SDCs) have emerged as a promising paradigm for hosting energy-intensive computing infrastructures in orbit, leveraging continuous solar energy and radiative cooling advantages. However, unlike ground facilities primarily constrained by power and site availability, SDCs are fundamentally limited by communication capability. The gap between petabit-scale internal data exchange in ground data centers and the gigabit-scale capacity of ground-space links forms a critical bottleneck. This article systematically analyzes communication constraints in SDC architectures and explores semantic communication as a key enabling paradigm. By transmitting compact, task-relevant semantic representations instead of raw data, uplink pressure can be substantially reduced. The feasibility of communication-efficient orbital AI infrastructures is demonstrated through the evaluation of a multi-layer heterogeneous SDC framework consisting of relay satellites and orbital computing nodes operating under coupled energy and thermal constraints. The article further outlines open research challenges toward scalable deployment.</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>semantic communication; semantic communications</t>
         </is>
       </c>
-      <c r="M11" t="b">
+      <c r="N11" t="b">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>not_detected</t>
-        </is>
-      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>source_error:papers_with_code</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>LLM / Agent 辅助语义通信</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>Foundation Model / LLM</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>6.5</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr">
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>2026-05-15T12:14:29.237809+00:00</t>
         </is>
@@ -1625,58 +1641,59 @@
           <t>Shannon's information theory deliberately excludes message semantics. This paper develops a rigorous framework for semantic communication that integrates formal proof systems with Shannon-theoretic tools. We introduce an axiomatic information model comprising Lsem-definable state sets linked by computable enabling maps, and define the semantic channel as a composition of Markov kernels whose supports respect the enabling structure. A fixed proof system induces an irredundant semantic core and a derivation-depth stratification, enabling four distortion measures of increasing semantic depth: Hamming, closure, depth, and a parameterized composite. Six families of computable semantic channel invariants are defined and their inter-relationships established, including a data processing bound, a semantic Fano bound, and an ideal-channel collapse theorem. The central quantitative result is a deductive compression gain: under closure-based fidelity, the minimum block length is determined by the irredundant core size rather than the full knowledge-base size. We instantiate the framework for heterogeneous multi-agent communication, introducing an overlap decomposition that yields necessary and sufficient conditions for closure-reliable communication. A semantic bottleneck phenomenon is identified in broadcast settings: vocabulary mismatch imposes irreducible fidelity limitations even over noiseless carriers. All results are verified on an explicit Datalog instance.</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
         <is>
           <t>DeepSC</t>
         </is>
       </c>
-      <c r="M12" t="b">
+      <c r="N12" t="b">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>not_detected</t>
-        </is>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>source_error:papers_with_code</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>LLM / Agent 辅助语义通信</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>Information Theory / Semantic Coding</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>6.5</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr">
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844805+00:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X12"/>
+  <autoFilter ref="A1:Y12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/weekly/semantic_communication_papers_2026-W20.xlsx
+++ b/outputs/weekly/semantic_communication_papers_2026-W20.xlsx
@@ -10,7 +10,7 @@
     <sheet name="papers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'papers'!$A$1:$Y$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'papers'!$A$1:$AA$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,17 +441,19 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,55 +529,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>open_source_status</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>code_url</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>project_url</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>candidate_code_urls</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>open_source_evidence</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>application_scenario</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>technical_framework</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>task_type</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>modality</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>relevance_score</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>curation_status</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>last_checked_at</t>
         </is>
@@ -640,43 +652,49 @@
       <c r="N2" t="b">
         <v>0</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>source_error:papers_with_code;source_error:pdf_link_extract</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>6G / 无线通信</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Optimization / Resource Allocation</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>13.5</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844757+00:00</t>
         </is>
@@ -741,43 +759,49 @@
       <c r="N3" t="b">
         <v>0</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>source_error:papers_with_code</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>任务导向通信</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>9.5</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-15T12:14:29.237416+00:00</t>
         </is>
@@ -842,43 +866,49 @@
       <c r="N4" t="b">
         <v>0</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>source_error:papers_with_code</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>6G / 无线通信</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Optimization / Resource Allocation</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Image</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>8</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-15T12:14:58.613259+00:00</t>
         </is>
@@ -943,43 +973,49 @@
       <c r="N5" t="b">
         <v>0</v>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>source_error:papers_with_code;source_error:pdf_link_extract</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>LLM / Agent 辅助语义通信</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Multi-Agent</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>分类/识别</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Image</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>7.5</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844490+00:00</t>
         </is>
@@ -1044,43 +1080,49 @@
       <c r="N6" t="b">
         <v>0</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>source_error:papers_with_code</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>LLM / Agent 辅助语义通信</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Foundation Model / LLM</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>生成</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>7.5</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844921+00:00</t>
         </is>
@@ -1145,43 +1187,49 @@
       <c r="N7" t="b">
         <v>0</v>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
         <is>
           <t>source_error:papers_with_code</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>6G / 无线通信</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Optimization / Resource Allocation</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>7</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-15T12:14:29.237651+00:00</t>
         </is>
@@ -1246,43 +1294,49 @@
       <c r="N8" t="b">
         <v>0</v>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>source_error:papers_with_code</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>source_error:papers_with_code;source_error:pdf_link_extract</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>任务导向通信</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>7</v>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-15T12:14:58.613325+00:00</t>
         </is>
@@ -1347,43 +1401,49 @@
       <c r="N9" t="b">
         <v>0</v>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>source_error:papers_with_code</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>6G / 无线通信</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>7</v>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844545+00:00</t>
         </is>
@@ -1448,43 +1508,49 @@
       <c r="N10" t="b">
         <v>0</v>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
         <is>
           <t>source_error:papers_with_code</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>6G / 无线通信</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Semantic-Aware Physical Layer</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>7</v>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844853+00:00</t>
         </is>
@@ -1549,43 +1615,49 @@
       <c r="N11" t="b">
         <v>0</v>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
         <is>
           <t>source_error:papers_with_code</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>LLM / Agent 辅助语义通信</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Foundation Model / LLM</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>6.5</v>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-15T12:14:29.237809+00:00</t>
         </is>
@@ -1650,50 +1722,56 @@
       <c r="N12" t="b">
         <v>0</v>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>not_detected</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
         <is>
           <t>source_error:papers_with_code</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>LLM / Agent 辅助语义通信</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Information Theory / Semantic Coding</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>传输</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>未标注</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>6.5</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>curated</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-15T12:17:24.844805+00:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y12"/>
+  <autoFilter ref="A1:AA12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/weekly/semantic_communication_papers_2026-W20.xlsx
+++ b/outputs/weekly/semantic_communication_papers_2026-W20.xlsx
@@ -444,8 +444,8 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="19" max="19"/>
     <col width="24" customWidth="1" min="20" max="20"/>
     <col width="24" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
@@ -876,7 +876,7 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>source_error:papers_with_code</t>
+          <t>source_error:papers_with_code;source_error:github_search</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1090,7 +1090,7 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>source_error:papers_with_code</t>
+          <t>source_error:papers_with_code;source_error:github_search</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1304,7 +1304,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>source_error:papers_with_code;source_error:pdf_link_extract</t>
+          <t>source_error:papers_with_code;source_error:github_search</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1518,7 +1518,7 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>source_error:papers_with_code</t>
+          <t>source_error:papers_with_code;source_error:github_search</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1732,7 +1732,7 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>source_error:papers_with_code</t>
+          <t>source_error:papers_with_code;source_error:github_search</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
